--- a/plantillas/excel_base.xlsx
+++ b/plantillas/excel_base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiante\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742D26A1-4183-4417-93C3-4D59C7962EFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB036A0-9BCD-43CB-B3B0-500D2035960D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="570" xr2:uid="{73D17D42-2032-4221-9DBF-D2EB2D99B5D8}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="570" activeTab="1" xr2:uid="{73D17D42-2032-4221-9DBF-D2EB2D99B5D8}"/>
   </bookViews>
   <sheets>
     <sheet name="MODIFICACIONES EN ASIGNATURAS" sheetId="1" r:id="rId1"/>
@@ -22,23 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="98">
   <si>
     <t>MODIFICACIÓN EN ASIGNATURAS DE LA MALLA CURRICULAR</t>
   </si>
@@ -145,9 +134,6 @@
     <t>MALLA CURRICULAR PROPUESTA</t>
   </si>
   <si>
-    <t>I SEMESTRE</t>
-  </si>
-  <si>
     <t>NIVEL 100 - I</t>
   </si>
   <si>
@@ -175,27 +161,18 @@
     <t>NIVEL 100 - II</t>
   </si>
   <si>
-    <t>II SEMESTRE</t>
-  </si>
-  <si>
     <t>NIVEL 200 - I</t>
   </si>
   <si>
     <t>NIVEL 200 - II</t>
   </si>
   <si>
-    <t>III SEMESTRE</t>
-  </si>
-  <si>
     <t>NIVEL 300 - I</t>
   </si>
   <si>
     <t>NIVEL 300 - II</t>
   </si>
   <si>
-    <t>IV SEMESTRE</t>
-  </si>
-  <si>
     <t>NIVEL 400 - I</t>
   </si>
   <si>
@@ -326,6 +303,24 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>I AÑO</t>
+  </si>
+  <si>
+    <t>II AÑO</t>
+  </si>
+  <si>
+    <t>III AÑO</t>
+  </si>
+  <si>
+    <t>IV AÑO</t>
+  </si>
+  <si>
+    <t>V AÑO</t>
+  </si>
+  <si>
+    <t>NIVEL 500 - I</t>
   </si>
 </sst>
 </file>
@@ -614,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -684,9 +679,69 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -696,102 +751,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -847,6 +842,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1330,38 +1334,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
     </row>
     <row r="2" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
     </row>
     <row r="3" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -1373,26 +1377,26 @@
       <c r="C3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="40"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="51"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="42" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="39" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -1401,20 +1405,20 @@
       <c r="E4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="54"/>
+      <c r="G4" s="37"/>
       <c r="H4" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="54"/>
+      <c r="K4" s="37"/>
       <c r="L4" s="9" t="s">
         <v>10</v>
       </c>
@@ -1426,9 +1430,9 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="42"/>
+      <c r="A5" s="46"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1439,11 +1443,11 @@
       <c r="G5" s="5">
         <v>3</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="31">
         <f>(G5+G6+G7)*16</f>
         <v>144</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="34">
         <f>H5/48</f>
         <v>3</v>
       </c>
@@ -1453,22 +1457,22 @@
       <c r="K5" s="5">
         <v>4</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="31">
         <f>(K5+K6+K7)*16</f>
         <v>144</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="34">
         <f>L5/48</f>
         <v>3</v>
       </c>
-      <c r="N5" s="45" t="s">
+      <c r="N5" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="42"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
@@ -1479,22 +1483,22 @@
       <c r="G6" s="5">
         <v>2</v>
       </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="52"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="35"/>
       <c r="J6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K6" s="5">
         <v>1</v>
       </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="46"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="43"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="43"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
@@ -1505,60 +1509,60 @@
       <c r="G7" s="5">
         <v>4</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="36"/>
       <c r="J7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K7" s="5">
         <v>4</v>
       </c>
-      <c r="L7" s="37"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="47"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="44"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="34"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="54"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="41" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="38" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="11"/>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="44"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="44" t="s">
+      <c r="J9" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="44"/>
+      <c r="K9" s="41"/>
       <c r="L9" s="9" t="s">
         <v>10</v>
       </c>
@@ -1570,9 +1574,9 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="42"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="4" t="s">
         <v>14</v>
       </c>
@@ -1585,11 +1589,11 @@
       <c r="G10" s="5">
         <v>2</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="31">
         <f>(G10+G11+G12)*16</f>
         <v>96</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="34">
         <f>H10/48</f>
         <v>2</v>
       </c>
@@ -1599,22 +1603,22 @@
       <c r="K10" s="5">
         <v>0</v>
       </c>
-      <c r="L10" s="35">
+      <c r="L10" s="31">
         <f>(K10+K11+K12)*16</f>
         <v>0</v>
       </c>
-      <c r="M10" s="51">
+      <c r="M10" s="34">
         <f>L10/48</f>
         <v>0</v>
       </c>
-      <c r="N10" s="45" t="s">
+      <c r="N10" s="42" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="42"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1625,22 +1629,22 @@
       <c r="G11" s="5">
         <v>2</v>
       </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="52"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="35"/>
       <c r="J11" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
-      <c r="L11" s="36"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="46"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="43"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="31"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="43"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="4" t="s">
         <v>19</v>
       </c>
@@ -1651,60 +1655,60 @@
       <c r="G12" s="5">
         <v>2</v>
       </c>
-      <c r="H12" s="37"/>
-      <c r="I12" s="53"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="36"/>
       <c r="J12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
       </c>
-      <c r="L12" s="37"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="47"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="44"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="34"/>
+      <c r="A13" s="52"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="54"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="41" t="s">
+      <c r="B14" s="31"/>
+      <c r="C14" s="38" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="50"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="49" t="s">
+      <c r="J14" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="50"/>
+      <c r="K14" s="48"/>
       <c r="L14" s="9" t="s">
         <v>10</v>
       </c>
@@ -1716,9 +1720,9 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="42"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="4" t="s">
         <v>14</v>
       </c>
@@ -1727,11 +1731,11 @@
         <v>15</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="35">
+      <c r="H15" s="31">
         <f>(G15+G16+G17)*16</f>
         <v>0</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="34">
         <f>H15/48</f>
         <v>0</v>
       </c>
@@ -1739,20 +1743,20 @@
         <v>15</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="35">
+      <c r="L15" s="31">
         <f>(K15+K16+K17)*16</f>
         <v>0</v>
       </c>
-      <c r="M15" s="51">
+      <c r="M15" s="34">
         <f>L15/48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="45"/>
+      <c r="N15" s="42"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="42"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="39"/>
       <c r="D16" s="4" t="s">
         <v>17</v>
       </c>
@@ -1761,20 +1765,20 @@
         <v>18</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="52"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="35"/>
       <c r="J16" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="46"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="43"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="43"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1783,58 +1787,58 @@
         <v>20</v>
       </c>
       <c r="G17" s="5"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="53"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="36"/>
       <c r="J17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="47"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="44"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="34"/>
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="54"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="41" t="s">
+      <c r="B19" s="31"/>
+      <c r="C19" s="38" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="44"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="44" t="s">
+      <c r="J19" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="44"/>
+      <c r="K19" s="41"/>
       <c r="L19" s="9" t="s">
         <v>10</v>
       </c>
@@ -1846,9 +1850,9 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="42"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="39"/>
       <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
@@ -1857,11 +1861,11 @@
         <v>15</v>
       </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="35">
+      <c r="H20" s="31">
         <f>(G20+G21+G22)*16</f>
         <v>0</v>
       </c>
-      <c r="I20" s="51">
+      <c r="I20" s="34">
         <f>H20/48</f>
         <v>0</v>
       </c>
@@ -1869,20 +1873,20 @@
         <v>15</v>
       </c>
       <c r="K20" s="5"/>
-      <c r="L20" s="35">
+      <c r="L20" s="31">
         <f>(K20+K21+K22)*16</f>
         <v>0</v>
       </c>
-      <c r="M20" s="51">
+      <c r="M20" s="34">
         <f>L20/48</f>
         <v>0</v>
       </c>
-      <c r="N20" s="45"/>
+      <c r="N20" s="42"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="31"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="39"/>
       <c r="D21" s="4" t="s">
         <v>17</v>
       </c>
@@ -1891,20 +1895,20 @@
         <v>18</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="52"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="35"/>
       <c r="J21" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="46"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="43"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="43"/>
+      <c r="A22" s="46"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="4" t="s">
         <v>19</v>
       </c>
@@ -1913,58 +1917,58 @@
         <v>20</v>
       </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="53"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="36"/>
       <c r="J22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K22" s="5"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="47"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="44"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="34"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="54"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="41" t="s">
+      <c r="B24" s="31"/>
+      <c r="C24" s="38" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E24" s="11"/>
-      <c r="F24" s="44" t="s">
+      <c r="F24" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="44"/>
+      <c r="G24" s="41"/>
       <c r="H24" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J24" s="44" t="s">
+      <c r="J24" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="K24" s="44"/>
+      <c r="K24" s="41"/>
       <c r="L24" s="9" t="s">
         <v>10</v>
       </c>
@@ -1976,9 +1980,9 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="42"/>
+      <c r="A25" s="46"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="39"/>
       <c r="D25" s="4" t="s">
         <v>14</v>
       </c>
@@ -1987,11 +1991,11 @@
         <v>15</v>
       </c>
       <c r="G25" s="5"/>
-      <c r="H25" s="35">
+      <c r="H25" s="31">
         <f>(G25+G26+G27)*16</f>
         <v>0</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="34">
         <f>H25/48</f>
         <v>0</v>
       </c>
@@ -1999,20 +2003,20 @@
         <v>15</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="35">
+      <c r="L25" s="31">
         <f>(K25+K26+K27)*16</f>
         <v>0</v>
       </c>
-      <c r="M25" s="51">
+      <c r="M25" s="34">
         <f>L25/48</f>
         <v>0</v>
       </c>
-      <c r="N25" s="45"/>
+      <c r="N25" s="42"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="31"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="42"/>
+      <c r="A26" s="46"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="39"/>
       <c r="D26" s="4" t="s">
         <v>17</v>
       </c>
@@ -2021,20 +2025,20 @@
         <v>18</v>
       </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="52"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="35"/>
       <c r="J26" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K26" s="5"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="46"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="43"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="31"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="46"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="4" t="s">
         <v>19</v>
       </c>
@@ -2043,58 +2047,58 @@
         <v>20</v>
       </c>
       <c r="G27" s="5"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="53"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="36"/>
       <c r="J27" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="47"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="44"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="32"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="34"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="54"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="41" t="s">
+      <c r="B29" s="31"/>
+      <c r="C29" s="38" t="s">
         <v>31</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E29" s="11"/>
-      <c r="F29" s="44" t="s">
+      <c r="F29" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="G29" s="44"/>
+      <c r="G29" s="41"/>
       <c r="H29" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="44" t="s">
+      <c r="J29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="K29" s="44"/>
+      <c r="K29" s="41"/>
       <c r="L29" s="9" t="s">
         <v>10</v>
       </c>
@@ -2106,9 +2110,9 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="31"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="42"/>
+      <c r="A30" s="46"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="39"/>
       <c r="D30" s="4" t="s">
         <v>14</v>
       </c>
@@ -2117,11 +2121,11 @@
         <v>15</v>
       </c>
       <c r="G30" s="5"/>
-      <c r="H30" s="35">
+      <c r="H30" s="31">
         <f>(G30+G31+G32)*16</f>
         <v>0</v>
       </c>
-      <c r="I30" s="51">
+      <c r="I30" s="34">
         <f>H30/48</f>
         <v>0</v>
       </c>
@@ -2129,20 +2133,20 @@
         <v>15</v>
       </c>
       <c r="K30" s="5"/>
-      <c r="L30" s="35">
+      <c r="L30" s="31">
         <f>(K30+K31+K32)*16</f>
         <v>0</v>
       </c>
-      <c r="M30" s="51">
+      <c r="M30" s="34">
         <f>L30/48</f>
         <v>0</v>
       </c>
-      <c r="N30" s="45"/>
+      <c r="N30" s="42"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="31"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="42"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="4" t="s">
         <v>17</v>
       </c>
@@ -2151,20 +2155,20 @@
         <v>18</v>
       </c>
       <c r="G31" s="5"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="52"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="35"/>
       <c r="J31" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K31" s="5"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="46"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="43"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="31"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="43"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="4" t="s">
         <v>19</v>
       </c>
@@ -2173,58 +2177,58 @@
         <v>20</v>
       </c>
       <c r="G32" s="5"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="53"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="36"/>
       <c r="J32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K32" s="5"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="47"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="44"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="34"/>
+      <c r="A33" s="52"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="54"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="41" t="s">
+      <c r="B34" s="31"/>
+      <c r="C34" s="38" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E34" s="11"/>
-      <c r="F34" s="44" t="s">
+      <c r="F34" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="44"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="44" t="s">
+      <c r="J34" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="44"/>
+      <c r="K34" s="41"/>
       <c r="L34" s="9" t="s">
         <v>10</v>
       </c>
@@ -2236,9 +2240,9 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="31"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="42"/>
+      <c r="A35" s="46"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="4" t="s">
         <v>14</v>
       </c>
@@ -2247,11 +2251,11 @@
         <v>15</v>
       </c>
       <c r="G35" s="5"/>
-      <c r="H35" s="35">
+      <c r="H35" s="31">
         <f>(G35+G36+G37)*16</f>
         <v>0</v>
       </c>
-      <c r="I35" s="51">
+      <c r="I35" s="34">
         <f>H35/48</f>
         <v>0</v>
       </c>
@@ -2259,20 +2263,20 @@
         <v>15</v>
       </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="35">
+      <c r="L35" s="31">
         <f>(K35+K36+K37)*16</f>
         <v>0</v>
       </c>
-      <c r="M35" s="51">
+      <c r="M35" s="34">
         <f>L35/48</f>
         <v>0</v>
       </c>
-      <c r="N35" s="45"/>
+      <c r="N35" s="42"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="31"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="42"/>
+      <c r="A36" s="46"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="39"/>
       <c r="D36" s="4" t="s">
         <v>17</v>
       </c>
@@ -2281,20 +2285,20 @@
         <v>18</v>
       </c>
       <c r="G36" s="5"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="52"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="35"/>
       <c r="J36" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K36" s="5"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="46"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="43"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="31"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="43"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="4" t="s">
         <v>19</v>
       </c>
@@ -2303,48 +2307,50 @@
         <v>20</v>
       </c>
       <c r="G37" s="5"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="53"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="36"/>
       <c r="J37" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="47"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="L20:L22"/>
-    <mergeCell ref="M20:M22"/>
-    <mergeCell ref="M30:M32"/>
-    <mergeCell ref="L25:L27"/>
-    <mergeCell ref="M25:M27"/>
-    <mergeCell ref="L30:L32"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="I30:I32"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="L10:L12"/>
-    <mergeCell ref="M10:M12"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="H35:H37"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="N25:N27"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="I35:I37"/>
-    <mergeCell ref="L35:L37"/>
-    <mergeCell ref="M35:M37"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A18:N18"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A33:N33"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="N35:N37"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="N30:N32"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="N10:N12"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
     <mergeCell ref="A1:N2"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A9:A12"/>
@@ -2361,38 +2367,36 @@
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="N20:N22"/>
     <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="N30:N32"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N10:N12"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A18:N18"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="A28:N28"/>
-    <mergeCell ref="A33:N33"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="N35:N37"/>
+    <mergeCell ref="H35:H37"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="N25:N27"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="I35:I37"/>
+    <mergeCell ref="L35:L37"/>
+    <mergeCell ref="M35:M37"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="L10:L12"/>
+    <mergeCell ref="M10:M12"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="I30:I32"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="L20:L22"/>
+    <mergeCell ref="M20:M22"/>
+    <mergeCell ref="M30:M32"/>
+    <mergeCell ref="L25:L27"/>
+    <mergeCell ref="M25:M27"/>
+    <mergeCell ref="L30:L32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2403,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D13E2D-6580-4A06-AB57-271518370837}">
-  <dimension ref="A1:BN53"/>
+  <dimension ref="A1:CF57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -2461,220 +2465,292 @@
     <col min="57" max="57" width="2.5703125" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="6.140625" customWidth="1"/>
-    <col min="60" max="60" width="11.42578125" customWidth="1"/>
-    <col min="61" max="61" width="10" customWidth="1"/>
-    <col min="62" max="62" width="10.28515625" customWidth="1"/>
-    <col min="63" max="63" width="9.85546875" customWidth="1"/>
-    <col min="64" max="256" width="11.42578125" customWidth="1"/>
+    <col min="60" max="60" width="6.5703125" customWidth="1"/>
+    <col min="61" max="61" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="5" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="6.140625" customWidth="1"/>
+    <col min="69" max="69" width="6.5703125" customWidth="1"/>
+    <col min="70" max="70" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="5" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="6.140625" customWidth="1"/>
+    <col min="78" max="78" width="11.42578125" customWidth="1"/>
+    <col min="79" max="79" width="10" customWidth="1"/>
+    <col min="80" max="80" width="10.28515625" customWidth="1"/>
+    <col min="81" max="81" width="9.85546875" customWidth="1"/>
+    <col min="82" max="274" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="65"/>
-      <c r="AG1" s="65"/>
-      <c r="AH1" s="65"/>
-      <c r="AI1" s="65"/>
-      <c r="AJ1" s="65"/>
-      <c r="AK1" s="65"/>
-      <c r="AL1" s="65"/>
-      <c r="AM1" s="65"/>
-      <c r="AN1" s="65"/>
-      <c r="AO1" s="65"/>
-      <c r="AP1" s="65"/>
-      <c r="AQ1" s="65"/>
-      <c r="AR1" s="65"/>
-      <c r="AS1" s="65"/>
-      <c r="AT1" s="65"/>
-      <c r="AU1" s="65"/>
-      <c r="AV1" s="65"/>
-      <c r="AW1" s="65"/>
-      <c r="AX1" s="65"/>
-      <c r="AY1" s="65"/>
-      <c r="AZ1" s="65"/>
-      <c r="BA1" s="65"/>
-      <c r="BB1" s="65"/>
-      <c r="BC1" s="65"/>
-      <c r="BD1" s="65"/>
-      <c r="BE1" s="65"/>
-      <c r="BF1" s="65"/>
-      <c r="BG1" s="65"/>
-      <c r="BH1" s="65"/>
-      <c r="BI1" s="65"/>
-      <c r="BJ1" s="65"/>
-      <c r="BK1" s="65"/>
-      <c r="BL1" s="65"/>
-      <c r="BM1" s="65"/>
-      <c r="BN1" s="65"/>
-    </row>
-    <row r="2" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="65"/>
-      <c r="AG2" s="65"/>
-      <c r="AH2" s="65"/>
-      <c r="AI2" s="65"/>
-      <c r="AJ2" s="65"/>
-      <c r="AK2" s="65"/>
-      <c r="AL2" s="65"/>
-      <c r="AM2" s="65"/>
-      <c r="AN2" s="65"/>
-      <c r="AO2" s="65"/>
-      <c r="AP2" s="65"/>
-      <c r="AQ2" s="65"/>
-      <c r="AR2" s="65"/>
-      <c r="AS2" s="65"/>
-      <c r="AT2" s="65"/>
-      <c r="AU2" s="65"/>
-      <c r="AV2" s="65"/>
-      <c r="AW2" s="65"/>
-      <c r="AX2" s="65"/>
-      <c r="AY2" s="65"/>
-      <c r="AZ2" s="65"/>
-      <c r="BA2" s="65"/>
-      <c r="BB2" s="65"/>
-      <c r="BC2" s="65"/>
-      <c r="BD2" s="65"/>
-      <c r="BE2" s="65"/>
-      <c r="BF2" s="65"/>
-      <c r="BG2" s="65"/>
-      <c r="BH2" s="65"/>
-      <c r="BI2" s="65"/>
-      <c r="BJ2" s="65"/>
-      <c r="BK2" s="65"/>
-      <c r="BL2" s="65"/>
-      <c r="BM2" s="65"/>
-      <c r="BN2" s="65"/>
-    </row>
-    <row r="3" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="65"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="65"/>
-      <c r="AL3" s="65"/>
-      <c r="AM3" s="65"/>
-      <c r="AN3" s="65"/>
-      <c r="AO3" s="65"/>
-      <c r="AP3" s="65"/>
-      <c r="AQ3" s="65"/>
-      <c r="AR3" s="65"/>
-      <c r="AS3" s="65"/>
-      <c r="AT3" s="65"/>
-      <c r="AU3" s="65"/>
-      <c r="AV3" s="65"/>
-      <c r="AW3" s="65"/>
-      <c r="AX3" s="65"/>
-      <c r="AY3" s="65"/>
-      <c r="AZ3" s="65"/>
-      <c r="BA3" s="65"/>
-      <c r="BB3" s="65"/>
-      <c r="BC3" s="65"/>
-      <c r="BD3" s="65"/>
-      <c r="BE3" s="65"/>
-      <c r="BF3" s="65"/>
-      <c r="BG3" s="65"/>
-      <c r="BH3" s="65"/>
-      <c r="BI3" s="65"/>
-      <c r="BJ3" s="65"/>
-      <c r="BK3" s="65"/>
-      <c r="BL3" s="65"/>
-      <c r="BM3" s="65"/>
-      <c r="BN3" s="65"/>
-    </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
+      <c r="AR1" s="60"/>
+      <c r="AS1" s="60"/>
+      <c r="AT1" s="60"/>
+      <c r="AU1" s="60"/>
+      <c r="AV1" s="60"/>
+      <c r="AW1" s="60"/>
+      <c r="AX1" s="60"/>
+      <c r="AY1" s="60"/>
+      <c r="AZ1" s="60"/>
+      <c r="BA1" s="60"/>
+      <c r="BB1" s="60"/>
+      <c r="BC1" s="60"/>
+      <c r="BD1" s="60"/>
+      <c r="BE1" s="60"/>
+      <c r="BF1" s="60"/>
+      <c r="BG1" s="60"/>
+      <c r="BH1" s="60"/>
+      <c r="BI1" s="60"/>
+      <c r="BJ1" s="60"/>
+      <c r="BK1" s="60"/>
+      <c r="BL1" s="60"/>
+      <c r="BM1" s="60"/>
+      <c r="BN1" s="60"/>
+      <c r="BO1" s="60"/>
+      <c r="BP1" s="60"/>
+      <c r="BQ1" s="60"/>
+      <c r="BR1" s="60"/>
+      <c r="BS1" s="60"/>
+      <c r="BT1" s="60"/>
+      <c r="BU1" s="60"/>
+      <c r="BV1" s="60"/>
+      <c r="BW1" s="60"/>
+      <c r="BX1" s="60"/>
+      <c r="BY1" s="60"/>
+      <c r="BZ1" s="60"/>
+      <c r="CA1" s="60"/>
+      <c r="CB1" s="60"/>
+      <c r="CC1" s="60"/>
+      <c r="CD1" s="60"/>
+      <c r="CE1" s="60"/>
+      <c r="CF1" s="60"/>
+    </row>
+    <row r="2" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="60"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="60"/>
+      <c r="AS2" s="60"/>
+      <c r="AT2" s="60"/>
+      <c r="AU2" s="60"/>
+      <c r="AV2" s="60"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="60"/>
+      <c r="AZ2" s="60"/>
+      <c r="BA2" s="60"/>
+      <c r="BB2" s="60"/>
+      <c r="BC2" s="60"/>
+      <c r="BD2" s="60"/>
+      <c r="BE2" s="60"/>
+      <c r="BF2" s="60"/>
+      <c r="BG2" s="60"/>
+      <c r="BH2" s="60"/>
+      <c r="BI2" s="60"/>
+      <c r="BJ2" s="60"/>
+      <c r="BK2" s="60"/>
+      <c r="BL2" s="60"/>
+      <c r="BM2" s="60"/>
+      <c r="BN2" s="60"/>
+      <c r="BO2" s="60"/>
+      <c r="BP2" s="60"/>
+      <c r="BQ2" s="60"/>
+      <c r="BR2" s="60"/>
+      <c r="BS2" s="60"/>
+      <c r="BT2" s="60"/>
+      <c r="BU2" s="60"/>
+      <c r="BV2" s="60"/>
+      <c r="BW2" s="60"/>
+      <c r="BX2" s="60"/>
+      <c r="BY2" s="60"/>
+      <c r="BZ2" s="60"/>
+      <c r="CA2" s="60"/>
+      <c r="CB2" s="60"/>
+      <c r="CC2" s="60"/>
+      <c r="CD2" s="60"/>
+      <c r="CE2" s="60"/>
+      <c r="CF2" s="60"/>
+    </row>
+    <row r="3" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="60"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="60"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="60"/>
+      <c r="AC3" s="60"/>
+      <c r="AD3" s="60"/>
+      <c r="AE3" s="60"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="60"/>
+      <c r="AJ3" s="60"/>
+      <c r="AK3" s="60"/>
+      <c r="AL3" s="60"/>
+      <c r="AM3" s="60"/>
+      <c r="AN3" s="60"/>
+      <c r="AO3" s="60"/>
+      <c r="AP3" s="60"/>
+      <c r="AQ3" s="60"/>
+      <c r="AR3" s="60"/>
+      <c r="AS3" s="60"/>
+      <c r="AT3" s="60"/>
+      <c r="AU3" s="60"/>
+      <c r="AV3" s="60"/>
+      <c r="AW3" s="60"/>
+      <c r="AX3" s="60"/>
+      <c r="AY3" s="60"/>
+      <c r="AZ3" s="60"/>
+      <c r="BA3" s="60"/>
+      <c r="BB3" s="60"/>
+      <c r="BC3" s="60"/>
+      <c r="BD3" s="60"/>
+      <c r="BE3" s="60"/>
+      <c r="BF3" s="60"/>
+      <c r="BG3" s="60"/>
+      <c r="BH3" s="60"/>
+      <c r="BI3" s="60"/>
+      <c r="BJ3" s="60"/>
+      <c r="BK3" s="60"/>
+      <c r="BL3" s="60"/>
+      <c r="BM3" s="60"/>
+      <c r="BN3" s="60"/>
+      <c r="BO3" s="60"/>
+      <c r="BP3" s="60"/>
+      <c r="BQ3" s="60"/>
+      <c r="BR3" s="60"/>
+      <c r="BS3" s="60"/>
+      <c r="BT3" s="60"/>
+      <c r="BU3" s="60"/>
+      <c r="BV3" s="60"/>
+      <c r="BW3" s="60"/>
+      <c r="BX3" s="60"/>
+      <c r="BY3" s="60"/>
+      <c r="BZ3" s="60"/>
+      <c r="CA3" s="60"/>
+      <c r="CB3" s="60"/>
+      <c r="CC3" s="60"/>
+      <c r="CD3" s="60"/>
+      <c r="CE3" s="60"/>
+      <c r="CF3" s="60"/>
+    </row>
+    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -2717,2101 +2793,2938 @@
       <c r="BC5" s="1"/>
       <c r="BD5" s="1"/>
       <c r="BE5" s="1"/>
-    </row>
-    <row r="6" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BI5" s="1"/>
+      <c r="BJ5" s="1"/>
+      <c r="BK5" s="1"/>
+      <c r="BL5" s="1"/>
+      <c r="BM5" s="1"/>
+      <c r="BN5" s="1"/>
+      <c r="BR5" s="1"/>
+      <c r="BS5" s="1"/>
+      <c r="BT5" s="1"/>
+      <c r="BU5" s="1"/>
+      <c r="BV5" s="1"/>
+      <c r="BW5" s="1"/>
+    </row>
+    <row r="6" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="57"/>
+      <c r="G6" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="60"/>
-      <c r="G6" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
       <c r="M6" s="1"/>
-      <c r="P6" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="56"/>
-      <c r="Y6" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="56"/>
-      <c r="AC6" s="56"/>
-      <c r="AD6" s="56"/>
+      <c r="P6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="58"/>
+      <c r="U6" s="58"/>
+      <c r="Y6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z6" s="58"/>
+      <c r="AA6" s="58"/>
+      <c r="AB6" s="58"/>
+      <c r="AC6" s="58"/>
+      <c r="AD6" s="58"/>
       <c r="AE6" s="1"/>
-      <c r="AH6" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI6" s="56"/>
-      <c r="AJ6" s="56"/>
-      <c r="AK6" s="56"/>
-      <c r="AL6" s="56"/>
-      <c r="AM6" s="56"/>
+      <c r="AH6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI6" s="58"/>
+      <c r="AJ6" s="58"/>
+      <c r="AK6" s="58"/>
+      <c r="AL6" s="58"/>
+      <c r="AM6" s="58"/>
       <c r="AN6" s="1"/>
-      <c r="AQ6" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR6" s="56"/>
-      <c r="AS6" s="56"/>
-      <c r="AT6" s="56"/>
-      <c r="AU6" s="56"/>
-      <c r="AV6" s="56"/>
+      <c r="AQ6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR6" s="58"/>
+      <c r="AS6" s="58"/>
+      <c r="AT6" s="58"/>
+      <c r="AU6" s="58"/>
+      <c r="AV6" s="58"/>
       <c r="AW6" s="1"/>
-      <c r="AZ6" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA6" s="56"/>
-      <c r="BB6" s="56"/>
-      <c r="BC6" s="56"/>
-      <c r="BD6" s="56"/>
-      <c r="BE6" s="56"/>
-    </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="AZ6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA6" s="58"/>
+      <c r="BB6" s="58"/>
+      <c r="BC6" s="58"/>
+      <c r="BD6" s="58"/>
+      <c r="BE6" s="58"/>
+      <c r="BI6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ6" s="58"/>
+      <c r="BK6" s="58"/>
+      <c r="BL6" s="58"/>
+      <c r="BM6" s="58"/>
+      <c r="BN6" s="58"/>
+      <c r="BR6" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS6" s="58"/>
+      <c r="BT6" s="58"/>
+      <c r="BU6" s="58"/>
+      <c r="BV6" s="58"/>
+      <c r="BW6" s="58"/>
+    </row>
+    <row r="7" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A7" s="63"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
       <c r="E7" s="23"/>
       <c r="G7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7" s="6">
         <v>3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" s="6">
         <v>2</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L7" s="6">
         <v>4</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N7">
         <f>(H7+J7+L7)/3</f>
         <v>3</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="6">
         <v>3</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S7" s="6">
         <v>2</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U7" s="6">
         <v>4</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W7">
         <f>(Q7+S7+U7)/3</f>
         <v>3</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z7" s="6">
         <v>3</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB7" s="6">
         <v>0</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD7" s="6">
         <v>6</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF7">
         <f>(Z7+AB7+AD7)/3</f>
         <v>3</v>
       </c>
       <c r="AH7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI7" s="6">
         <v>3</v>
       </c>
       <c r="AJ7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK7" s="6">
         <v>1</v>
       </c>
       <c r="AL7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM7" s="6">
         <v>5</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO7">
         <f>(AI7+AK7+AM7)/3</f>
         <v>3</v>
       </c>
       <c r="AQ7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR7" s="6">
         <v>1</v>
       </c>
       <c r="AS7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT7" s="6">
         <v>1</v>
       </c>
       <c r="AU7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV7" s="6">
         <v>1</v>
       </c>
       <c r="AW7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX7">
         <f>(AR7+AT7+AV7)/3</f>
         <v>1</v>
       </c>
       <c r="AZ7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA7" s="6">
         <v>2</v>
       </c>
       <c r="BB7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC7" s="6">
         <v>2</v>
       </c>
       <c r="BD7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE7" s="6">
         <v>2</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG7">
         <f>(BA7+BC7+BE7)/3</f>
         <v>2</v>
       </c>
       <c r="BI7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BJ7" s="6">
-        <f>H7+Q7+Z7+AI7+AR7+BA7</f>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="BK7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BL7" s="6">
-        <f>J7+S7+AB7+AK7+AT7+BC7</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BN7" s="6">
-        <f>L7+U7+AD7+AM7+AV7+BE7</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="BO7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP7">
+        <f>(BJ7+BL7+BN7)/3</f>
+        <v>2</v>
+      </c>
+      <c r="BR7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BX7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY7">
+        <f>(BS7+BU7+BW7)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB7" s="6">
+        <f>H7+Q7+Z7+AI7+AR7+BA7+BJ7+BS7</f>
+        <v>17</v>
+      </c>
+      <c r="CC7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD7" s="6">
+        <f>J7+S7+AB7+AK7+AT7+BC7+BL7+BU7</f>
+        <v>10</v>
+      </c>
+      <c r="CE7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF7" s="6">
+        <f>L7+U7+AD7+AM7+AV7+BE7+BN7+BW7</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A8" s="63"/>
-      <c r="BI8" s="57" t="s">
+      <c r="CA8" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB8" s="61"/>
+      <c r="CC8" s="61"/>
+      <c r="CD8" s="61"/>
+      <c r="CE8" s="61"/>
+      <c r="CF8" s="3">
+        <f>(CB7+CD7+CF7)*16</f>
+        <v>816</v>
+      </c>
+    </row>
+    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A9" s="63"/>
+      <c r="CA9" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ8" s="57"/>
-      <c r="BK8" s="57"/>
-      <c r="BL8" s="57"/>
-      <c r="BM8" s="57"/>
-      <c r="BN8" s="3">
-        <f>(BJ7+BL7+BN7)*16</f>
-        <v>720</v>
-      </c>
-    </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A9" s="63"/>
-      <c r="BI9" s="58" t="s">
+      <c r="CB9" s="56"/>
+      <c r="CC9" s="56"/>
+      <c r="CD9" s="56"/>
+      <c r="CE9" s="57"/>
+      <c r="CF9" s="3">
+        <f>CF8/48</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="63"/>
+      <c r="B10" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="BJ9" s="59"/>
-      <c r="BK9" s="59"/>
-      <c r="BL9" s="59"/>
-      <c r="BM9" s="60"/>
-      <c r="BN9" s="3">
-        <f>BN8/48</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="63"/>
-      <c r="B10" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60"/>
-      <c r="G10" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="57"/>
+      <c r="G10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
       <c r="M10" s="1"/>
-      <c r="P10" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="Y10" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z10" s="56"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="56"/>
-      <c r="AC10" s="56"/>
-      <c r="AD10" s="56"/>
+      <c r="P10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="58"/>
+      <c r="S10" s="58"/>
+      <c r="T10" s="58"/>
+      <c r="U10" s="58"/>
+      <c r="Y10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" s="58"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="58"/>
+      <c r="AC10" s="58"/>
+      <c r="AD10" s="58"/>
       <c r="AE10" s="1"/>
-      <c r="AH10" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI10" s="56"/>
-      <c r="AJ10" s="56"/>
-      <c r="AK10" s="56"/>
-      <c r="AL10" s="56"/>
-      <c r="AM10" s="56"/>
+      <c r="AH10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI10" s="58"/>
+      <c r="AJ10" s="58"/>
+      <c r="AK10" s="58"/>
+      <c r="AL10" s="58"/>
+      <c r="AM10" s="58"/>
       <c r="AN10" s="1"/>
-      <c r="AQ10" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR10" s="56"/>
-      <c r="AS10" s="56"/>
-      <c r="AT10" s="56"/>
-      <c r="AU10" s="56"/>
-      <c r="AV10" s="56"/>
+      <c r="AQ10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR10" s="58"/>
+      <c r="AS10" s="58"/>
+      <c r="AT10" s="58"/>
+      <c r="AU10" s="58"/>
+      <c r="AV10" s="58"/>
       <c r="AW10" s="1"/>
-      <c r="AZ10" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA10" s="56"/>
-      <c r="BB10" s="56"/>
-      <c r="BC10" s="56"/>
-      <c r="BD10" s="56"/>
-      <c r="BE10" s="56"/>
-    </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="AZ10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA10" s="58"/>
+      <c r="BB10" s="58"/>
+      <c r="BC10" s="58"/>
+      <c r="BD10" s="58"/>
+      <c r="BE10" s="58"/>
+      <c r="BI10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ10" s="58"/>
+      <c r="BK10" s="58"/>
+      <c r="BL10" s="58"/>
+      <c r="BM10" s="58"/>
+      <c r="BN10" s="58"/>
+      <c r="BR10" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS10" s="58"/>
+      <c r="BT10" s="58"/>
+      <c r="BU10" s="58"/>
+      <c r="BV10" s="58"/>
+      <c r="BW10" s="58"/>
+    </row>
+    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A11" s="63"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
       <c r="G11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N11">
         <f>(H11+J11+L11)/3</f>
         <v>0</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q11" s="6"/>
       <c r="R11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S11" s="6"/>
       <c r="T11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U11" s="6"/>
       <c r="V11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W11">
         <f>(Q11+S11+U11)/3</f>
         <v>0</v>
       </c>
       <c r="Y11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z11" s="6"/>
       <c r="AA11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB11" s="6"/>
       <c r="AC11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD11" s="6"/>
       <c r="AE11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF11">
         <f>(Z11+AB11+AD11)/3</f>
         <v>0</v>
       </c>
       <c r="AH11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI11" s="6"/>
       <c r="AJ11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK11" s="6"/>
       <c r="AL11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM11" s="6"/>
       <c r="AN11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO11">
         <f>(AI11+AK11+AM11)/3</f>
         <v>0</v>
       </c>
       <c r="AQ11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR11" s="6"/>
       <c r="AS11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT11" s="6"/>
       <c r="AU11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV11" s="6"/>
       <c r="AW11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX11">
         <f>(AR11+AT11+AV11)/3</f>
         <v>0</v>
       </c>
       <c r="AZ11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA11" s="6"/>
       <c r="BB11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC11" s="6"/>
       <c r="BD11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE11" s="6"/>
       <c r="BF11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG11">
         <f>(BA11+BC11+BE11)/3</f>
         <v>0</v>
       </c>
       <c r="BI11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BJ11" s="6">
-        <f>H11+Q11+Z11+AI11+AR11+BA11</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="BJ11" s="6"/>
       <c r="BK11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL11" s="6">
-        <f>J11+S11+AB11+AK11+AT11+BC11</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BL11" s="6"/>
       <c r="BM11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN11" s="6">
-        <f>L11+U11+AD11+AM11+AV11+BE11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="BN11" s="6"/>
+      <c r="BO11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP11">
+        <f>(BJ11+BL11+BN11)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS11" s="6"/>
+      <c r="BT11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU11" s="6"/>
+      <c r="BV11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW11" s="6"/>
+      <c r="BX11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY11">
+        <f>(BS11+BU11+BW11)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB11" s="6">
+        <f>H11+Q11+Z11+AI11+AR11+BA11+BJ11+BS11</f>
+        <v>0</v>
+      </c>
+      <c r="CC11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD11" s="6">
+        <f>J11+S11+AB11+AK11+AT11+BC11+BL11+BU11</f>
+        <v>0</v>
+      </c>
+      <c r="CE11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF11" s="6">
+        <f>L11+U11+AD11+AM11+AV11+BE11+BN11+BW11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A12" s="63"/>
-      <c r="BI12" s="57" t="s">
+      <c r="CA12" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB12" s="61"/>
+      <c r="CC12" s="61"/>
+      <c r="CD12" s="61"/>
+      <c r="CE12" s="61"/>
+      <c r="CF12" s="3">
+        <f>(CB11+CD11+CF11)*16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A13" s="64"/>
+      <c r="CA13" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ12" s="57"/>
-      <c r="BK12" s="57"/>
-      <c r="BL12" s="57"/>
-      <c r="BM12" s="57"/>
-      <c r="BN12" s="3">
-        <f>(BJ11+BL11+BN11)*16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A13" s="64"/>
-      <c r="BI13" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ13" s="59"/>
-      <c r="BK13" s="59"/>
-      <c r="BL13" s="59"/>
-      <c r="BM13" s="60"/>
-      <c r="BN13" s="3">
-        <f>BN12/48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CB13" s="56"/>
+      <c r="CC13" s="56"/>
+      <c r="CD13" s="56"/>
+      <c r="CE13" s="57"/>
+      <c r="CF13" s="3">
+        <f>CF12/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="60"/>
-      <c r="G14" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="56"/>
-      <c r="L14" s="56"/>
+        <v>93</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="57"/>
+      <c r="G14" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
       <c r="M14" s="1"/>
-      <c r="P14" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q14" s="56"/>
-      <c r="R14" s="56"/>
-      <c r="S14" s="56"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="56"/>
-      <c r="Y14" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z14" s="56"/>
-      <c r="AA14" s="56"/>
-      <c r="AB14" s="56"/>
-      <c r="AC14" s="56"/>
-      <c r="AD14" s="56"/>
+      <c r="P14" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q14" s="58"/>
+      <c r="R14" s="58"/>
+      <c r="S14" s="58"/>
+      <c r="T14" s="58"/>
+      <c r="U14" s="58"/>
+      <c r="Y14" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z14" s="58"/>
+      <c r="AA14" s="58"/>
+      <c r="AB14" s="58"/>
+      <c r="AC14" s="58"/>
+      <c r="AD14" s="58"/>
       <c r="AE14" s="1"/>
-      <c r="AH14" s="56"/>
-      <c r="AI14" s="56"/>
-      <c r="AJ14" s="56"/>
-      <c r="AK14" s="56"/>
-      <c r="AL14" s="56"/>
-      <c r="AM14" s="56"/>
+      <c r="AH14" s="58"/>
+      <c r="AI14" s="58"/>
+      <c r="AJ14" s="58"/>
+      <c r="AK14" s="58"/>
+      <c r="AL14" s="58"/>
+      <c r="AM14" s="58"/>
       <c r="AN14" s="1"/>
-      <c r="AQ14" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR14" s="56"/>
-      <c r="AS14" s="56"/>
-      <c r="AT14" s="56"/>
-      <c r="AU14" s="56"/>
-      <c r="AV14" s="56"/>
+      <c r="AQ14" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR14" s="58"/>
+      <c r="AS14" s="58"/>
+      <c r="AT14" s="58"/>
+      <c r="AU14" s="58"/>
+      <c r="AV14" s="58"/>
       <c r="AW14" s="1"/>
-      <c r="AZ14" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA14" s="56"/>
-      <c r="BB14" s="56"/>
-      <c r="BC14" s="56"/>
-      <c r="BD14" s="56"/>
-      <c r="BE14" s="56"/>
-    </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="AZ14" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA14" s="58"/>
+      <c r="BB14" s="58"/>
+      <c r="BC14" s="58"/>
+      <c r="BD14" s="58"/>
+      <c r="BE14" s="58"/>
+      <c r="BI14" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ14" s="58"/>
+      <c r="BK14" s="58"/>
+      <c r="BL14" s="58"/>
+      <c r="BM14" s="58"/>
+      <c r="BN14" s="58"/>
+      <c r="BR14" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS14" s="58"/>
+      <c r="BT14" s="58"/>
+      <c r="BU14" s="58"/>
+      <c r="BV14" s="58"/>
+      <c r="BW14" s="58"/>
+    </row>
+    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A15" s="63"/>
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="G15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N15">
         <f>(H15+J15+L15)/3</f>
         <v>0</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S15" s="6"/>
       <c r="T15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U15" s="6"/>
       <c r="V15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W15">
         <f>(Q15+S15+U15)/3</f>
         <v>0</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z15" s="6"/>
       <c r="AA15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB15" s="6"/>
       <c r="AC15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD15" s="6"/>
       <c r="AE15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF15">
         <f>(Z15+AB15+AD15)/3</f>
         <v>0</v>
       </c>
       <c r="AH15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI15" s="6"/>
       <c r="AJ15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK15" s="6"/>
       <c r="AL15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM15" s="6"/>
       <c r="AN15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO15">
         <f>(AI15+AK15+AM15)/3</f>
         <v>0</v>
       </c>
       <c r="AQ15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR15" s="6"/>
       <c r="AS15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT15" s="6"/>
       <c r="AU15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV15" s="6"/>
       <c r="AW15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX15">
         <f>(AR15+AT15+AV15)/3</f>
         <v>0</v>
       </c>
       <c r="AZ15" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA15" s="6"/>
       <c r="BB15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC15" s="6"/>
       <c r="BD15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE15" s="6"/>
       <c r="BF15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG15">
         <f>(BA15+BC15+BE15)/3</f>
         <v>0</v>
       </c>
       <c r="BI15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BJ15" s="6">
-        <f>H15+Q15+Z15+AI15+AR15+BA15</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="BJ15" s="6"/>
       <c r="BK15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL15" s="6">
-        <f>J15+S15+AB15+AK15+AT15+BC15</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BL15" s="6"/>
       <c r="BM15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN15" s="6">
-        <f>L15+U15+AD15+AM15+AV15+BE15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="BN15" s="6"/>
+      <c r="BO15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP15">
+        <f>(BJ15+BL15+BN15)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS15" s="6"/>
+      <c r="BT15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU15" s="6"/>
+      <c r="BV15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW15" s="6"/>
+      <c r="BX15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY15">
+        <f>(BS15+BU15+BW15)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB15" s="6">
+        <f>H15+Q15+Z15+AI15+AR15+BA15+BJ15+BS15</f>
+        <v>0</v>
+      </c>
+      <c r="CC15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD15" s="6">
+        <f>J15+S15+AB15+AK15+AT15+BC15+BL15+BU15</f>
+        <v>0</v>
+      </c>
+      <c r="CE15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF15" s="6">
+        <f>L15+U15+AD15+AM15+AV15+BE15+BN15+BW15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A16" s="63"/>
-      <c r="BI16" s="57" t="s">
+      <c r="CA16" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB16" s="61"/>
+      <c r="CC16" s="61"/>
+      <c r="CD16" s="61"/>
+      <c r="CE16" s="61"/>
+      <c r="CF16" s="3">
+        <f>CB15+CD15+CF15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A17" s="63"/>
+      <c r="CA17" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ16" s="57"/>
-      <c r="BK16" s="57"/>
-      <c r="BL16" s="57"/>
-      <c r="BM16" s="57"/>
-      <c r="BN16" s="3">
-        <f>BJ15+BL15+BN15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A17" s="63"/>
-      <c r="BI17" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ17" s="59"/>
-      <c r="BK17" s="59"/>
-      <c r="BL17" s="59"/>
-      <c r="BM17" s="60"/>
-      <c r="BN17" s="3">
-        <f>BN16/48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CB17" s="56"/>
+      <c r="CC17" s="56"/>
+      <c r="CD17" s="56"/>
+      <c r="CE17" s="57"/>
+      <c r="CF17" s="3">
+        <f>CF16/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="63"/>
-      <c r="B18" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="60"/>
-      <c r="G18" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="56"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="56"/>
-      <c r="L18" s="56"/>
+      <c r="B18" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="57"/>
+      <c r="G18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
       <c r="M18" s="1"/>
-      <c r="P18" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q18" s="56"/>
-      <c r="R18" s="56"/>
-      <c r="S18" s="56"/>
-      <c r="T18" s="56"/>
-      <c r="U18" s="56"/>
-      <c r="Y18" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z18" s="56"/>
-      <c r="AA18" s="56"/>
-      <c r="AB18" s="56"/>
-      <c r="AC18" s="56"/>
-      <c r="AD18" s="56"/>
+      <c r="P18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="58"/>
+      <c r="Y18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z18" s="58"/>
+      <c r="AA18" s="58"/>
+      <c r="AB18" s="58"/>
+      <c r="AC18" s="58"/>
+      <c r="AD18" s="58"/>
       <c r="AE18" s="1"/>
-      <c r="AH18" s="56"/>
-      <c r="AI18" s="56"/>
-      <c r="AJ18" s="56"/>
-      <c r="AK18" s="56"/>
-      <c r="AL18" s="56"/>
-      <c r="AM18" s="56"/>
+      <c r="AH18" s="58"/>
+      <c r="AI18" s="58"/>
+      <c r="AJ18" s="58"/>
+      <c r="AK18" s="58"/>
+      <c r="AL18" s="58"/>
+      <c r="AM18" s="58"/>
       <c r="AN18" s="1"/>
-      <c r="AQ18" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR18" s="56"/>
-      <c r="AS18" s="56"/>
-      <c r="AT18" s="56"/>
-      <c r="AU18" s="56"/>
-      <c r="AV18" s="56"/>
+      <c r="AQ18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR18" s="58"/>
+      <c r="AS18" s="58"/>
+      <c r="AT18" s="58"/>
+      <c r="AU18" s="58"/>
+      <c r="AV18" s="58"/>
       <c r="AW18" s="1"/>
-      <c r="AZ18" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA18" s="56"/>
-      <c r="BB18" s="56"/>
-      <c r="BC18" s="56"/>
-      <c r="BD18" s="56"/>
-      <c r="BE18" s="56"/>
-    </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="AZ18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA18" s="58"/>
+      <c r="BB18" s="58"/>
+      <c r="BC18" s="58"/>
+      <c r="BD18" s="58"/>
+      <c r="BE18" s="58"/>
+      <c r="BI18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ18" s="58"/>
+      <c r="BK18" s="58"/>
+      <c r="BL18" s="58"/>
+      <c r="BM18" s="58"/>
+      <c r="BN18" s="58"/>
+      <c r="BR18" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS18" s="58"/>
+      <c r="BT18" s="58"/>
+      <c r="BU18" s="58"/>
+      <c r="BV18" s="58"/>
+      <c r="BW18" s="58"/>
+    </row>
+    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A19" s="63"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
       <c r="G19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N19">
         <f>(H19+J19+L19)/3</f>
         <v>0</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q19" s="6"/>
       <c r="R19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S19" s="6"/>
       <c r="T19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U19" s="6"/>
       <c r="V19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W19">
         <f>(Q19+S19+U19)/3</f>
         <v>0</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD19" s="6"/>
       <c r="AE19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF19">
         <f>(Z19+AB19+AD19)/3</f>
         <v>0</v>
       </c>
       <c r="AH19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI19" s="6"/>
       <c r="AJ19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK19" s="6"/>
       <c r="AL19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM19" s="6"/>
       <c r="AN19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO19">
         <f>(AI19+AK19+AM19)/3</f>
         <v>0</v>
       </c>
       <c r="AQ19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR19" s="6"/>
       <c r="AS19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT19" s="6"/>
       <c r="AU19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV19" s="6"/>
       <c r="AW19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX19">
         <f>(AR19+AT19+AV19)/3</f>
         <v>0</v>
       </c>
       <c r="AZ19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA19" s="6"/>
       <c r="BB19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC19" s="6"/>
       <c r="BD19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE19" s="6"/>
       <c r="BF19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG19">
         <f>(BA19+BC19+BE19)/3</f>
         <v>0</v>
       </c>
       <c r="BI19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BJ19" s="6">
-        <f>H19+Q19+Z19+AI19+AR19+BA19</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="BJ19" s="6"/>
       <c r="BK19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL19" s="6">
-        <f>J19+S19+AB19+AK19+AT19+BC19</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BL19" s="6"/>
       <c r="BM19" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN19" s="6">
-        <f>L19+U19+AD19+AM19+AV19+BE19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="BN19" s="6"/>
+      <c r="BO19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP19">
+        <f>(BJ19+BL19+BN19)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS19" s="6"/>
+      <c r="BT19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU19" s="6"/>
+      <c r="BV19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW19" s="6"/>
+      <c r="BX19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY19">
+        <f>(BS19+BU19+BW19)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB19" s="6">
+        <f>H19+Q19+Z19+AI19+AR19+BA19+BJ19+BS19</f>
+        <v>0</v>
+      </c>
+      <c r="CC19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD19" s="6">
+        <f>J19+S19+AB19+AK19+AT19+BC19+BL19+BU19</f>
+        <v>0</v>
+      </c>
+      <c r="CE19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF19" s="6">
+        <f>L19+U19+AD19+AM19+AV19+BE19+BN19+BW19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A20" s="63"/>
-      <c r="BI20" s="57" t="s">
+      <c r="CA20" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB20" s="61"/>
+      <c r="CC20" s="61"/>
+      <c r="CD20" s="61"/>
+      <c r="CE20" s="61"/>
+      <c r="CF20" s="3">
+        <f>CB19+CD19+CF19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A21" s="64"/>
+      <c r="CA21" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ20" s="57"/>
-      <c r="BK20" s="57"/>
-      <c r="BL20" s="57"/>
-      <c r="BM20" s="57"/>
-      <c r="BN20" s="3">
-        <f>BJ19+BL19+BN19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A21" s="64"/>
-      <c r="BI21" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ21" s="59"/>
-      <c r="BK21" s="59"/>
-      <c r="BL21" s="59"/>
-      <c r="BM21" s="60"/>
-      <c r="BN21" s="3">
-        <f>BN20/48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CB21" s="56"/>
+      <c r="CC21" s="56"/>
+      <c r="CD21" s="56"/>
+      <c r="CE21" s="57"/>
+      <c r="CF21" s="3">
+        <f>CF20/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="62" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="60"/>
-      <c r="G22" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H22" s="56"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="56"/>
+        <v>94</v>
+      </c>
+      <c r="B22" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
+      <c r="G22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
       <c r="M22" s="1"/>
-      <c r="P22" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q22" s="56"/>
-      <c r="R22" s="56"/>
-      <c r="S22" s="56"/>
-      <c r="T22" s="56"/>
-      <c r="U22" s="56"/>
-      <c r="Y22" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z22" s="56"/>
-      <c r="AA22" s="56"/>
-      <c r="AB22" s="56"/>
-      <c r="AC22" s="56"/>
-      <c r="AD22" s="56"/>
+      <c r="P22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="58"/>
+      <c r="S22" s="58"/>
+      <c r="T22" s="58"/>
+      <c r="U22" s="58"/>
+      <c r="Y22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z22" s="58"/>
+      <c r="AA22" s="58"/>
+      <c r="AB22" s="58"/>
+      <c r="AC22" s="58"/>
+      <c r="AD22" s="58"/>
       <c r="AE22" s="1"/>
-      <c r="AH22" s="56"/>
-      <c r="AI22" s="56"/>
-      <c r="AJ22" s="56"/>
-      <c r="AK22" s="56"/>
-      <c r="AL22" s="56"/>
-      <c r="AM22" s="56"/>
+      <c r="AH22" s="58"/>
+      <c r="AI22" s="58"/>
+      <c r="AJ22" s="58"/>
+      <c r="AK22" s="58"/>
+      <c r="AL22" s="58"/>
+      <c r="AM22" s="58"/>
       <c r="AN22" s="1"/>
-      <c r="AQ22" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR22" s="56"/>
-      <c r="AS22" s="56"/>
-      <c r="AT22" s="56"/>
-      <c r="AU22" s="56"/>
-      <c r="AV22" s="56"/>
+      <c r="AQ22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR22" s="58"/>
+      <c r="AS22" s="58"/>
+      <c r="AT22" s="58"/>
+      <c r="AU22" s="58"/>
+      <c r="AV22" s="58"/>
       <c r="AW22" s="1"/>
-      <c r="AZ22" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA22" s="56"/>
-      <c r="BB22" s="56"/>
-      <c r="BC22" s="56"/>
-      <c r="BD22" s="56"/>
-      <c r="BE22" s="56"/>
-    </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="AZ22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA22" s="58"/>
+      <c r="BB22" s="58"/>
+      <c r="BC22" s="58"/>
+      <c r="BD22" s="58"/>
+      <c r="BE22" s="58"/>
+      <c r="BI22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ22" s="58"/>
+      <c r="BK22" s="58"/>
+      <c r="BL22" s="58"/>
+      <c r="BM22" s="58"/>
+      <c r="BN22" s="58"/>
+      <c r="BR22" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS22" s="58"/>
+      <c r="BT22" s="58"/>
+      <c r="BU22" s="58"/>
+      <c r="BV22" s="58"/>
+      <c r="BW22" s="58"/>
+    </row>
+    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A23" s="63"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
       <c r="G23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N23">
         <f>(H23+J23+L23)/3</f>
         <v>0</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S23" s="6"/>
       <c r="T23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U23" s="6"/>
       <c r="V23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W23">
         <f>(Q23+S23+U23)/3</f>
         <v>0</v>
       </c>
       <c r="Y23" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z23" s="6"/>
       <c r="AA23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD23" s="6"/>
       <c r="AE23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF23">
         <f>(Z23+AB23+AD23)/3</f>
         <v>0</v>
       </c>
       <c r="AH23" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI23" s="6"/>
       <c r="AJ23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK23" s="6"/>
       <c r="AL23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM23" s="6"/>
       <c r="AN23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO23">
         <f>(AI23+AK23+AM23)/3</f>
         <v>0</v>
       </c>
       <c r="AQ23" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR23" s="6"/>
       <c r="AS23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT23" s="6"/>
       <c r="AU23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV23" s="6"/>
       <c r="AW23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX23">
         <f>(AR23+AT23+AV23)/3</f>
         <v>0</v>
       </c>
       <c r="AZ23" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA23" s="6"/>
       <c r="BB23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC23" s="6"/>
       <c r="BD23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE23" s="6"/>
       <c r="BF23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG23">
         <f>(BA23+BC23+BE23)/3</f>
         <v>0</v>
       </c>
       <c r="BI23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BJ23" s="6">
-        <f>H23+Q23+Z23+AI23+AR23+BA23</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="BJ23" s="6"/>
       <c r="BK23" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL23" s="6">
-        <f>J23+S23+AB23+AK23+AT23+BC23</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BL23" s="6"/>
       <c r="BM23" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN23" s="6">
-        <f>L23+U23+AD23+AM23+AV23+BE23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="BN23" s="6"/>
+      <c r="BO23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP23">
+        <f>(BJ23+BL23+BN23)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS23" s="6"/>
+      <c r="BT23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU23" s="6"/>
+      <c r="BV23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW23" s="6"/>
+      <c r="BX23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY23">
+        <f>(BS23+BU23+BW23)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB23" s="6">
+        <f>H23+Q23+Z23+AI23+AR23+BA23+BJ23+BS23</f>
+        <v>0</v>
+      </c>
+      <c r="CC23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD23" s="6">
+        <f>J23+S23+AB23+AK23+AT23+BC23+BL23+BU23</f>
+        <v>0</v>
+      </c>
+      <c r="CE23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF23" s="6">
+        <f>L23+U23+AD23+AM23+AV23+BE23+BN23+BW23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A24" s="63"/>
-      <c r="BI24" s="57" t="s">
+      <c r="CA24" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB24" s="61"/>
+      <c r="CC24" s="61"/>
+      <c r="CD24" s="61"/>
+      <c r="CE24" s="61"/>
+      <c r="CF24" s="3">
+        <f>CB23+CD23+CF23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A25" s="63"/>
+      <c r="CA25" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ24" s="57"/>
-      <c r="BK24" s="57"/>
-      <c r="BL24" s="57"/>
-      <c r="BM24" s="57"/>
-      <c r="BN24" s="3">
-        <f>BJ23+BL23+BN23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A25" s="63"/>
-      <c r="BI25" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ25" s="59"/>
-      <c r="BK25" s="59"/>
-      <c r="BL25" s="59"/>
-      <c r="BM25" s="60"/>
-      <c r="BN25" s="3">
-        <f>BN24/48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CB25" s="56"/>
+      <c r="CC25" s="56"/>
+      <c r="CD25" s="56"/>
+      <c r="CE25" s="57"/>
+      <c r="CF25" s="3">
+        <f>CF24/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="63"/>
-      <c r="B26" s="58" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="60"/>
-      <c r="G26" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
+      <c r="B26" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="57"/>
+      <c r="G26" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
       <c r="M26" s="1"/>
-      <c r="P26" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="56"/>
-      <c r="T26" s="56"/>
-      <c r="U26" s="56"/>
-      <c r="Y26" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z26" s="56"/>
-      <c r="AA26" s="56"/>
-      <c r="AB26" s="56"/>
-      <c r="AC26" s="56"/>
-      <c r="AD26" s="56"/>
+      <c r="P26" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="58"/>
+      <c r="S26" s="58"/>
+      <c r="T26" s="58"/>
+      <c r="U26" s="58"/>
+      <c r="Y26" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z26" s="58"/>
+      <c r="AA26" s="58"/>
+      <c r="AB26" s="58"/>
+      <c r="AC26" s="58"/>
+      <c r="AD26" s="58"/>
       <c r="AE26" s="1"/>
-      <c r="AH26" s="56"/>
-      <c r="AI26" s="56"/>
-      <c r="AJ26" s="56"/>
-      <c r="AK26" s="56"/>
-      <c r="AL26" s="56"/>
-      <c r="AM26" s="56"/>
+      <c r="AH26" s="58"/>
+      <c r="AI26" s="58"/>
+      <c r="AJ26" s="58"/>
+      <c r="AK26" s="58"/>
+      <c r="AL26" s="58"/>
+      <c r="AM26" s="58"/>
       <c r="AN26" s="1"/>
-      <c r="AQ26" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR26" s="56"/>
-      <c r="AS26" s="56"/>
-      <c r="AT26" s="56"/>
-      <c r="AU26" s="56"/>
-      <c r="AV26" s="56"/>
+      <c r="AQ26" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR26" s="58"/>
+      <c r="AS26" s="58"/>
+      <c r="AT26" s="58"/>
+      <c r="AU26" s="58"/>
+      <c r="AV26" s="58"/>
       <c r="AW26" s="1"/>
-      <c r="AZ26" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA26" s="56"/>
-      <c r="BB26" s="56"/>
-      <c r="BC26" s="56"/>
-      <c r="BD26" s="56"/>
-      <c r="BE26" s="56"/>
-    </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="AZ26" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA26" s="58"/>
+      <c r="BB26" s="58"/>
+      <c r="BC26" s="58"/>
+      <c r="BD26" s="58"/>
+      <c r="BE26" s="58"/>
+      <c r="BI26" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ26" s="58"/>
+      <c r="BK26" s="58"/>
+      <c r="BL26" s="58"/>
+      <c r="BM26" s="58"/>
+      <c r="BN26" s="58"/>
+      <c r="BR26" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS26" s="58"/>
+      <c r="BT26" s="58"/>
+      <c r="BU26" s="58"/>
+      <c r="BV26" s="58"/>
+      <c r="BW26" s="58"/>
+    </row>
+    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A27" s="63"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
       <c r="G27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N27">
         <f>(H27+J27+L27)/3</f>
         <v>0</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q27" s="6"/>
       <c r="R27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S27" s="6"/>
       <c r="T27" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U27" s="6"/>
       <c r="V27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W27">
         <f>(Q27+S27+U27)/3</f>
         <v>0</v>
       </c>
       <c r="Y27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z27" s="6"/>
       <c r="AA27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB27" s="6"/>
       <c r="AC27" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD27" s="6"/>
       <c r="AE27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF27">
         <f>(Z27+AB27+AD27)/3</f>
         <v>0</v>
       </c>
       <c r="AH27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI27" s="6"/>
       <c r="AJ27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK27" s="6"/>
       <c r="AL27" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM27" s="6"/>
       <c r="AN27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO27">
         <f>(AI27+AK27+AM27)/3</f>
         <v>0</v>
       </c>
       <c r="AQ27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR27" s="6"/>
       <c r="AS27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT27" s="6"/>
       <c r="AU27" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV27" s="6"/>
       <c r="AW27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX27">
         <f>(AR27+AT27+AV27)/3</f>
         <v>0</v>
       </c>
       <c r="AZ27" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA27" s="6"/>
       <c r="BB27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC27" s="6"/>
       <c r="BD27" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE27" s="6"/>
       <c r="BF27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG27">
         <f>(BA27+BC27+BE27)/3</f>
         <v>0</v>
       </c>
       <c r="BI27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BJ27" s="6">
-        <f>H27+Q27+Z27+AI27+AR27+BA27</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="BJ27" s="6"/>
       <c r="BK27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL27" s="6">
-        <f>J27+S27+AB27+AK27+AT27+BC27</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BL27" s="6"/>
       <c r="BM27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN27" s="6">
-        <f>L27+U27+AD27+AM27+AV27+BE27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="BN27" s="6"/>
+      <c r="BO27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP27">
+        <f>(BJ27+BL27+BN27)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS27" s="6"/>
+      <c r="BT27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU27" s="6"/>
+      <c r="BV27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW27" s="6"/>
+      <c r="BX27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY27">
+        <f>(BS27+BU27+BW27)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB27" s="6">
+        <f>H27+Q27+Z27+AI27+AR27+BA27+BJ27+BS27</f>
+        <v>0</v>
+      </c>
+      <c r="CC27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD27" s="6">
+        <f>J27+S27+AB27+AK27+AT27+BC27+BL27+BU27</f>
+        <v>0</v>
+      </c>
+      <c r="CE27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF27" s="6">
+        <f>L27+U27+AD27+AM27+AV27+BE27+BN27+BW27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A28" s="63"/>
-      <c r="BI28" s="57" t="s">
+      <c r="CA28" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB28" s="61"/>
+      <c r="CC28" s="61"/>
+      <c r="CD28" s="61"/>
+      <c r="CE28" s="61"/>
+      <c r="CF28" s="3">
+        <f>CB27+CD27+CF27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A29" s="64"/>
+      <c r="CA29" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ28" s="57"/>
-      <c r="BK28" s="57"/>
-      <c r="BL28" s="57"/>
-      <c r="BM28" s="57"/>
-      <c r="BN28" s="3">
-        <f>BJ27+BL27+BN27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
-      <c r="BI29" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ29" s="59"/>
-      <c r="BK29" s="59"/>
-      <c r="BL29" s="59"/>
-      <c r="BM29" s="60"/>
-      <c r="BN29" s="3">
-        <f>BN28/48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="60"/>
-      <c r="G30" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
+      <c r="CB29" s="56"/>
+      <c r="CC29" s="56"/>
+      <c r="CD29" s="56"/>
+      <c r="CE29" s="57"/>
+      <c r="CF29" s="3">
+        <f>CF28/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="G30" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
       <c r="M30" s="1"/>
-      <c r="P30" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q30" s="56"/>
-      <c r="R30" s="56"/>
-      <c r="S30" s="56"/>
-      <c r="T30" s="56"/>
-      <c r="U30" s="56"/>
-      <c r="Y30" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z30" s="56"/>
-      <c r="AA30" s="56"/>
-      <c r="AB30" s="56"/>
-      <c r="AC30" s="56"/>
-      <c r="AD30" s="56"/>
+      <c r="P30" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="58"/>
+      <c r="S30" s="58"/>
+      <c r="T30" s="58"/>
+      <c r="U30" s="58"/>
+      <c r="Y30" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z30" s="58"/>
+      <c r="AA30" s="58"/>
+      <c r="AB30" s="58"/>
+      <c r="AC30" s="58"/>
+      <c r="AD30" s="58"/>
       <c r="AE30" s="1"/>
-      <c r="AH30" s="56"/>
-      <c r="AI30" s="56"/>
-      <c r="AJ30" s="56"/>
-      <c r="AK30" s="56"/>
-      <c r="AL30" s="56"/>
-      <c r="AM30" s="56"/>
+      <c r="AH30" s="58"/>
+      <c r="AI30" s="58"/>
+      <c r="AJ30" s="58"/>
+      <c r="AK30" s="58"/>
+      <c r="AL30" s="58"/>
+      <c r="AM30" s="58"/>
       <c r="AN30" s="1"/>
-      <c r="AQ30" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR30" s="56"/>
-      <c r="AS30" s="56"/>
-      <c r="AT30" s="56"/>
-      <c r="AU30" s="56"/>
-      <c r="AV30" s="56"/>
+      <c r="AQ30" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR30" s="58"/>
+      <c r="AS30" s="58"/>
+      <c r="AT30" s="58"/>
+      <c r="AU30" s="58"/>
+      <c r="AV30" s="58"/>
       <c r="AW30" s="1"/>
-      <c r="AZ30" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA30" s="56"/>
-      <c r="BB30" s="56"/>
-      <c r="BC30" s="56"/>
-      <c r="BD30" s="56"/>
-      <c r="BE30" s="56"/>
-    </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A31" s="66"/>
+      <c r="AZ30" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA30" s="58"/>
+      <c r="BB30" s="58"/>
+      <c r="BC30" s="58"/>
+      <c r="BD30" s="58"/>
+      <c r="BE30" s="58"/>
+      <c r="BI30" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ30" s="58"/>
+      <c r="BK30" s="58"/>
+      <c r="BL30" s="58"/>
+      <c r="BM30" s="58"/>
+      <c r="BN30" s="58"/>
+      <c r="BR30" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS30" s="58"/>
+      <c r="BT30" s="58"/>
+      <c r="BU30" s="58"/>
+      <c r="BV30" s="58"/>
+      <c r="BW30" s="58"/>
+    </row>
+    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A31" s="59"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="G31" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N31">
         <f>(H31+J31+L31)/3</f>
         <v>0</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S31" s="6"/>
       <c r="T31" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U31" s="6"/>
       <c r="V31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W31">
         <f>(Q31+S31+U31)/3</f>
         <v>0</v>
       </c>
       <c r="Y31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z31" s="6"/>
       <c r="AA31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB31" s="6"/>
       <c r="AC31" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD31" s="6"/>
       <c r="AE31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF31">
         <f>(Z31+AB31+AD31)/3</f>
         <v>0</v>
       </c>
       <c r="AH31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI31" s="6"/>
       <c r="AJ31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK31" s="6"/>
       <c r="AL31" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM31" s="6"/>
       <c r="AN31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO31">
         <f>(AI31+AK31+AM31)/3</f>
         <v>0</v>
       </c>
       <c r="AQ31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR31" s="6"/>
       <c r="AS31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT31" s="6"/>
       <c r="AU31" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV31" s="6"/>
       <c r="AW31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX31">
         <f>(AR31+AT31+AV31)/3</f>
         <v>0</v>
       </c>
       <c r="AZ31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA31" s="6"/>
       <c r="BB31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC31" s="6"/>
       <c r="BD31" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE31" s="6"/>
       <c r="BF31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG31">
         <f>(BA31+BC31+BE31)/3</f>
         <v>0</v>
       </c>
       <c r="BI31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BJ31" s="6">
-        <f>H31+Q31+Z31+AI31+AR31+BA31</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="BJ31" s="6"/>
       <c r="BK31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL31" s="6">
-        <f>J31+S31+AB31+AK31+AT31+BC31</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BL31" s="6"/>
       <c r="BM31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN31" s="6">
-        <f>L31+U31+AD31+AM31+AV31+BE31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A32" s="66"/>
-      <c r="BI32" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="BN31" s="6"/>
+      <c r="BO31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP31">
+        <f>(BJ31+BL31+BN31)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS31" s="6"/>
+      <c r="BT31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU31" s="6"/>
+      <c r="BV31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW31" s="6"/>
+      <c r="BX31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY31">
+        <f>(BS31+BU31+BW31)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB31" s="6">
+        <f>H31+Q31+Z31+AI31+AR31+BA31+BJ31+BS31</f>
+        <v>0</v>
+      </c>
+      <c r="CC31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD31" s="6">
+        <f>J31+S31+AB31+AK31+AT31+BC31+BL31+BU31</f>
+        <v>0</v>
+      </c>
+      <c r="CE31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF31" s="6">
+        <f>L31+U31+AD31+AM31+AV31+BE31+BN31+BW31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A32" s="59"/>
+      <c r="CA32" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB32" s="61"/>
+      <c r="CC32" s="61"/>
+      <c r="CD32" s="61"/>
+      <c r="CE32" s="61"/>
+      <c r="CF32" s="3">
+        <f>CB31+CD31+CF31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A33" s="59"/>
+      <c r="CA33" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ32" s="57"/>
-      <c r="BK32" s="57"/>
-      <c r="BL32" s="57"/>
-      <c r="BM32" s="57"/>
-      <c r="BN32" s="3">
-        <f>BJ31+BL31+BN31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A33" s="66"/>
-      <c r="BI33" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ33" s="59"/>
-      <c r="BK33" s="59"/>
-      <c r="BL33" s="59"/>
-      <c r="BM33" s="60"/>
-      <c r="BN33" s="3">
-        <f>BN32/48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="66"/>
-      <c r="B34" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="59"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="60"/>
-      <c r="G34" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
+      <c r="CB33" s="56"/>
+      <c r="CC33" s="56"/>
+      <c r="CD33" s="56"/>
+      <c r="CE33" s="57"/>
+      <c r="CF33" s="3">
+        <f>CF32/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59"/>
+      <c r="B34" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="57"/>
+      <c r="G34" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
       <c r="M34" s="1"/>
-      <c r="P34" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q34" s="56"/>
-      <c r="R34" s="56"/>
-      <c r="S34" s="56"/>
-      <c r="T34" s="56"/>
-      <c r="U34" s="56"/>
-      <c r="Y34" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z34" s="56"/>
-      <c r="AA34" s="56"/>
-      <c r="AB34" s="56"/>
-      <c r="AC34" s="56"/>
-      <c r="AD34" s="56"/>
+      <c r="P34" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="58"/>
+      <c r="S34" s="58"/>
+      <c r="T34" s="58"/>
+      <c r="U34" s="58"/>
+      <c r="Y34" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z34" s="58"/>
+      <c r="AA34" s="58"/>
+      <c r="AB34" s="58"/>
+      <c r="AC34" s="58"/>
+      <c r="AD34" s="58"/>
       <c r="AE34" s="1"/>
-      <c r="AH34" s="56"/>
-      <c r="AI34" s="56"/>
-      <c r="AJ34" s="56"/>
-      <c r="AK34" s="56"/>
-      <c r="AL34" s="56"/>
-      <c r="AM34" s="56"/>
+      <c r="AH34" s="58"/>
+      <c r="AI34" s="58"/>
+      <c r="AJ34" s="58"/>
+      <c r="AK34" s="58"/>
+      <c r="AL34" s="58"/>
+      <c r="AM34" s="58"/>
       <c r="AN34" s="1"/>
-      <c r="AQ34" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="AR34" s="56"/>
-      <c r="AS34" s="56"/>
-      <c r="AT34" s="56"/>
-      <c r="AU34" s="56"/>
-      <c r="AV34" s="56"/>
+      <c r="AQ34" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR34" s="58"/>
+      <c r="AS34" s="58"/>
+      <c r="AT34" s="58"/>
+      <c r="AU34" s="58"/>
+      <c r="AV34" s="58"/>
       <c r="AW34" s="1"/>
-      <c r="AZ34" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="BA34" s="56"/>
-      <c r="BB34" s="56"/>
-      <c r="BC34" s="56"/>
-      <c r="BD34" s="56"/>
-      <c r="BE34" s="56"/>
-    </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A35" s="66"/>
+      <c r="AZ34" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA34" s="58"/>
+      <c r="BB34" s="58"/>
+      <c r="BC34" s="58"/>
+      <c r="BD34" s="58"/>
+      <c r="BE34" s="58"/>
+      <c r="BI34" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ34" s="58"/>
+      <c r="BK34" s="58"/>
+      <c r="BL34" s="58"/>
+      <c r="BM34" s="58"/>
+      <c r="BN34" s="58"/>
+      <c r="BR34" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS34" s="58"/>
+      <c r="BT34" s="58"/>
+      <c r="BU34" s="58"/>
+      <c r="BV34" s="58"/>
+      <c r="BW34" s="58"/>
+    </row>
+    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A35" s="59"/>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
       <c r="G35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N35">
         <f>(H35+J35+L35)/3</f>
         <v>0</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q35" s="6"/>
       <c r="R35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S35" s="6"/>
       <c r="T35" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U35" s="6"/>
       <c r="V35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W35">
         <f>(Q35+S35+U35)/3</f>
         <v>0</v>
       </c>
       <c r="Y35" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z35" s="6"/>
       <c r="AA35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB35" s="6"/>
       <c r="AC35" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF35">
         <f>(Z35+AB35+AD35)/3</f>
         <v>0</v>
       </c>
       <c r="AH35" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AI35" s="6"/>
       <c r="AJ35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AK35" s="6"/>
       <c r="AL35" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AM35" s="6"/>
       <c r="AN35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AO35">
         <f>(AI35+AK35+AM35)/3</f>
         <v>0</v>
       </c>
       <c r="AQ35" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AR35" s="6"/>
       <c r="AS35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT35" s="6"/>
       <c r="AU35" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AV35" s="6"/>
       <c r="AW35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX35">
         <f>(AR35+AT35+AV35)/3</f>
         <v>0</v>
       </c>
       <c r="AZ35" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BA35" s="6"/>
       <c r="BB35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BC35" s="6"/>
       <c r="BD35" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BE35" s="6"/>
       <c r="BF35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BG35">
         <f>(BA35+BC35+BE35)/3</f>
         <v>0</v>
       </c>
       <c r="BI35" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BJ35" s="6">
-        <f>H35+Q35+Z35+AI35+AR35+BA35</f>
-        <v>0</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="BJ35" s="6"/>
       <c r="BK35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="BL35" s="6">
-        <f>J35+S35+AB35+AK35+AT35+BC35</f>
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="BL35" s="6"/>
       <c r="BM35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN35" s="6">
-        <f>L35+U35+AD35+AM35+AV35+BE35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A36" s="66"/>
-      <c r="BI36" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="BN35" s="6"/>
+      <c r="BO35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP35">
+        <f>(BJ35+BL35+BN35)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS35" s="6"/>
+      <c r="BT35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU35" s="6"/>
+      <c r="BV35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW35" s="6"/>
+      <c r="BX35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY35">
+        <f>(BS35+BU35+BW35)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB35" s="6">
+        <f>H35+Q35+Z35+AI35+AR35+BA35+BJ35+BS35</f>
+        <v>0</v>
+      </c>
+      <c r="CC35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD35" s="6">
+        <f>J35+S35+AB35+AK35+AT35+BC35+BL35+BU35</f>
+        <v>0</v>
+      </c>
+      <c r="CE35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF35" s="6">
+        <f>L35+U35+AD35+AM35+AV35+BE35+BN35+BW35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A36" s="59"/>
+      <c r="CA36" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB36" s="61"/>
+      <c r="CC36" s="61"/>
+      <c r="CD36" s="61"/>
+      <c r="CE36" s="61"/>
+      <c r="CF36" s="3">
+        <f>CB35+CD35+CF35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A37" s="59"/>
+      <c r="CA37" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="BJ36" s="57"/>
-      <c r="BK36" s="57"/>
-      <c r="BL36" s="57"/>
-      <c r="BM36" s="57"/>
-      <c r="BN36" s="3">
-        <f>BJ35+BL35+BN35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A37" s="66"/>
-      <c r="BI37" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ37" s="59"/>
-      <c r="BK37" s="59"/>
-      <c r="BL37" s="59"/>
-      <c r="BM37" s="60"/>
-      <c r="BN37" s="3">
-        <f>BN36/48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G39" s="2" t="s">
+      <c r="CB37" s="56"/>
+      <c r="CC37" s="56"/>
+      <c r="CD37" s="56"/>
+      <c r="CE37" s="57"/>
+      <c r="CF37" s="3">
+        <f>CF36/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="G38" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="87"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="87"/>
+      <c r="K38" s="87"/>
+      <c r="L38" s="88"/>
+      <c r="M38" s="1"/>
+      <c r="P38" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q38" s="87"/>
+      <c r="R38" s="87"/>
+      <c r="S38" s="87"/>
+      <c r="T38" s="87"/>
+      <c r="U38" s="88"/>
+      <c r="Y38" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z38" s="87"/>
+      <c r="AA38" s="87"/>
+      <c r="AB38" s="87"/>
+      <c r="AC38" s="87"/>
+      <c r="AD38" s="88"/>
+      <c r="AE38" s="1"/>
+      <c r="AH38" s="86"/>
+      <c r="AI38" s="87"/>
+      <c r="AJ38" s="87"/>
+      <c r="AK38" s="87"/>
+      <c r="AL38" s="87"/>
+      <c r="AM38" s="88"/>
+      <c r="AN38" s="1"/>
+      <c r="AQ38" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR38" s="87"/>
+      <c r="AS38" s="87"/>
+      <c r="AT38" s="87"/>
+      <c r="AU38" s="87"/>
+      <c r="AV38" s="88"/>
+      <c r="AW38" s="1"/>
+      <c r="AZ38" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA38" s="87"/>
+      <c r="BB38" s="87"/>
+      <c r="BC38" s="87"/>
+      <c r="BD38" s="87"/>
+      <c r="BE38" s="88"/>
+      <c r="BI38" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ38" s="87"/>
+      <c r="BK38" s="87"/>
+      <c r="BL38" s="87"/>
+      <c r="BM38" s="87"/>
+      <c r="BN38" s="88"/>
+      <c r="BR38" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS38" s="87"/>
+      <c r="BT38" s="87"/>
+      <c r="BU38" s="87"/>
+      <c r="BV38" s="87"/>
+      <c r="BW38" s="88"/>
+    </row>
+    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A39" s="59"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="G39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L39" s="6"/>
+      <c r="M39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39">
+        <f>(H39+J39+L39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="U39" s="6"/>
+      <c r="V39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W39">
+        <f>(Q39+S39+U39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF39">
+        <f>(Z39+AB39+AD39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI39" s="6"/>
+      <c r="AJ39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK39" s="6"/>
+      <c r="AL39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM39" s="6"/>
+      <c r="AN39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO39">
+        <f>(AI39+AK39+AM39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AR39" s="6"/>
+      <c r="AS39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AT39" s="6"/>
+      <c r="AU39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AV39" s="6"/>
+      <c r="AW39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AX39">
+        <f>(AR39+AT39+AV39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="AZ39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BA39" s="6"/>
+      <c r="BB39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BC39" s="6"/>
+      <c r="BD39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BE39" s="6"/>
+      <c r="BF39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BG39">
+        <f>(BA39+BC39+BE39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BI39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BJ39" s="6"/>
+      <c r="BK39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BL39" s="6"/>
+      <c r="BM39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BN39" s="6"/>
+      <c r="BO39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BP39">
+        <f>(BJ39+BL39+BN39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="BR39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS39" s="6"/>
+      <c r="BT39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BU39" s="6"/>
+      <c r="BV39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="BW39" s="6"/>
+      <c r="BX39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="BY39">
+        <f>(BS39+BU39+BW39)/3</f>
+        <v>0</v>
+      </c>
+      <c r="CA39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB39" s="6">
+        <f>H39+Q39+Z39+AI39+AR39+BA39+BJ39+BS39</f>
+        <v>0</v>
+      </c>
+      <c r="CC39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="CD39" s="6">
+        <f>J39+S39+AB39+AK39+AT39+BC39+BL39+BU39</f>
+        <v>0</v>
+      </c>
+      <c r="CE39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="CF39" s="6">
+        <f>L39+U39+AD39+AM39+AV39+BE39+BN39+BW39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A40" s="59"/>
+      <c r="CA40" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="CB40" s="56"/>
+      <c r="CC40" s="56"/>
+      <c r="CD40" s="56"/>
+      <c r="CE40" s="57"/>
+      <c r="CF40" s="3">
+        <f>CB39+CD39+CF39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A41" s="59"/>
+      <c r="CA41" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="CB41" s="56"/>
+      <c r="CC41" s="56"/>
+      <c r="CD41" s="56"/>
+      <c r="CE41" s="57"/>
+      <c r="CF41" s="3">
+        <f>CF40/48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="G43" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="61" t="s">
+      <c r="H43" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+    </row>
+    <row r="44" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="G44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+    </row>
+    <row r="45" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="G45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+    </row>
+    <row r="46" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="G46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="19"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="19"/>
+      <c r="CA46" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="61"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="61"/>
-      <c r="O39" s="61"/>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="61"/>
-    </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" s="19" t="s">
+      <c r="CB46" s="66"/>
+      <c r="CC46" s="66"/>
+      <c r="CD46" s="66"/>
+      <c r="CE46" s="66"/>
+      <c r="CF46">
+        <f>CB19+CB23+CB27+CB31+CB35+CB15+CB11+CB7+CB39</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CA47" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-    </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G41" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="19" t="s">
+      <c r="CB47" s="66"/>
+      <c r="CC47" s="66"/>
+      <c r="CD47" s="66"/>
+      <c r="CE47" s="66"/>
+      <c r="CF47">
+        <f>CD19+CD23+CD27+CD31+CD35+CD15+CD11+CD7+CD39</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="H48" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-    </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="19" t="s">
+      <c r="CA48" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
-      <c r="BI42" s="55" t="s">
+      <c r="CB48" s="66"/>
+      <c r="CC48" s="66"/>
+      <c r="CD48" s="66"/>
+      <c r="CE48" s="66"/>
+      <c r="CF48">
+        <f>CF19+CF23+CF27+CF31+CF35+CF15+CF11+CF7+CF39</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G49" s="24"/>
+      <c r="H49" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="BJ42" s="55"/>
-      <c r="BK42" s="55"/>
-      <c r="BL42" s="55"/>
-      <c r="BM42" s="55"/>
-      <c r="BN42">
-        <f>BJ19+BJ23+BJ27+BJ31+BJ35+BJ15+BJ11+BJ7</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="BI43" s="55" t="s">
+      <c r="CA49" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="BJ43" s="55"/>
-      <c r="BK43" s="55"/>
-      <c r="BL43" s="55"/>
-      <c r="BM43" s="55"/>
-      <c r="BN43">
-        <f>BL19+BL23+BL27+BL31+BL35+BL15+BL11+BL7</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="H44" s="19" t="s">
+      <c r="CB49" s="66"/>
+      <c r="CC49" s="66"/>
+      <c r="CD49" s="66"/>
+      <c r="CE49" s="66"/>
+    </row>
+    <row r="50" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G50" s="25"/>
+      <c r="H50" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="BI44" s="55" t="s">
+      <c r="CA50" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="BJ44" s="55"/>
-      <c r="BK44" s="55"/>
-      <c r="BL44" s="55"/>
-      <c r="BM44" s="55"/>
-      <c r="BN44">
-        <f>BN19+BN23+BN27+BN31+BN35+BN15+BN11+BN7</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G45" s="24"/>
-      <c r="H45" s="19" t="s">
+      <c r="CB50" s="66"/>
+      <c r="CC50" s="66"/>
+      <c r="CD50" s="66"/>
+      <c r="CE50" s="66"/>
+    </row>
+    <row r="51" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G51" s="26"/>
+      <c r="H51" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="BI45" s="55" t="s">
+      <c r="CA51" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="BJ45" s="55"/>
-      <c r="BK45" s="55"/>
-      <c r="BL45" s="55"/>
-      <c r="BM45" s="55"/>
-    </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G46" s="25"/>
-      <c r="H46" s="19" t="s">
+      <c r="CB51" s="66"/>
+      <c r="CC51" s="66"/>
+      <c r="CD51" s="66"/>
+      <c r="CE51" s="66"/>
+    </row>
+    <row r="52" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G52" s="27"/>
+      <c r="H52" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="BI46" s="55" t="s">
+      <c r="CA52" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="BJ46" s="55"/>
-      <c r="BK46" s="55"/>
-      <c r="BL46" s="55"/>
-      <c r="BM46" s="55"/>
-    </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G47" s="26"/>
-      <c r="H47" s="19" t="s">
+      <c r="CB52" s="13"/>
+      <c r="CC52" s="13"/>
+      <c r="CD52" s="13"/>
+      <c r="CE52" s="13"/>
+      <c r="CF52">
+        <f>CF46+CF47+CF48+CF49+CF50+CF51</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G53" s="28"/>
+      <c r="H53" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="BI47" s="55" t="s">
+      <c r="CA53" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="BJ47" s="55"/>
-      <c r="BK47" s="55"/>
-      <c r="BL47" s="55"/>
-      <c r="BM47" s="55"/>
-    </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="G48" s="27"/>
-      <c r="H48" s="19" t="s">
+      <c r="CB53" s="13"/>
+      <c r="CC53" s="13"/>
+      <c r="CD53" s="13"/>
+      <c r="CE53" s="13"/>
+      <c r="CF53">
+        <f>CF52/48</f>
+        <v>1.0625</v>
+      </c>
+    </row>
+    <row r="54" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G54" s="29"/>
+      <c r="H54" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="BI48" s="13" t="s">
+    </row>
+    <row r="55" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G55" s="30"/>
+      <c r="H55" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="BJ48" s="13"/>
-      <c r="BK48" s="13"/>
-      <c r="BL48" s="13"/>
-      <c r="BM48" s="13"/>
-      <c r="BN48">
-        <f>BN42+BN43+BN44+BN45+BN46+BN47</f>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="7:66" x14ac:dyDescent="0.25">
-      <c r="G49" s="28"/>
-      <c r="H49" s="19" t="s">
+    </row>
+    <row r="56" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="G56" s="30"/>
+      <c r="H56" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="BI49" s="13" t="s">
+    </row>
+    <row r="57" spans="7:84" x14ac:dyDescent="0.25">
+      <c r="X57" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BJ49" s="13"/>
-      <c r="BK49" s="13"/>
-      <c r="BL49" s="13"/>
-      <c r="BM49" s="13"/>
-      <c r="BN49">
-        <f>BN48/48</f>
-        <v>0.9375</v>
-      </c>
-    </row>
-    <row r="50" spans="7:66" x14ac:dyDescent="0.25">
-      <c r="G50" s="29"/>
-      <c r="H50" s="19" t="s">
+      <c r="AK57" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="51" spans="7:66" x14ac:dyDescent="0.25">
-      <c r="G51" s="30"/>
-      <c r="H51" s="19" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="7:66" x14ac:dyDescent="0.25">
-      <c r="G52" s="30"/>
-      <c r="H52" s="19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="7:66" x14ac:dyDescent="0.25">
-      <c r="X53" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK53" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AL53" s="2"/>
+      <c r="AL57" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="112">
+    <mergeCell ref="CA40:CE40"/>
+    <mergeCell ref="CA41:CE41"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="G38:L38"/>
+    <mergeCell ref="P38:U38"/>
+    <mergeCell ref="Y38:AD38"/>
+    <mergeCell ref="AH38:AM38"/>
+    <mergeCell ref="BR18:BW18"/>
+    <mergeCell ref="BR22:BW22"/>
+    <mergeCell ref="BR26:BW26"/>
+    <mergeCell ref="BR30:BW30"/>
+    <mergeCell ref="BR34:BW34"/>
+    <mergeCell ref="BI18:BN18"/>
+    <mergeCell ref="BI22:BN22"/>
+    <mergeCell ref="BI26:BN26"/>
+    <mergeCell ref="BI30:BN30"/>
+    <mergeCell ref="BI34:BN34"/>
+    <mergeCell ref="CA50:CE50"/>
+    <mergeCell ref="CA51:CE51"/>
+    <mergeCell ref="Y26:AD26"/>
+    <mergeCell ref="AH26:AM26"/>
+    <mergeCell ref="AQ26:AV26"/>
+    <mergeCell ref="CA32:CE32"/>
+    <mergeCell ref="CA33:CE33"/>
+    <mergeCell ref="AZ26:BE26"/>
+    <mergeCell ref="CA48:CE48"/>
+    <mergeCell ref="CA28:CE28"/>
+    <mergeCell ref="CA29:CE29"/>
+    <mergeCell ref="AQ30:AV30"/>
+    <mergeCell ref="AZ30:BE30"/>
+    <mergeCell ref="CA49:CE49"/>
+    <mergeCell ref="CA36:CE36"/>
+    <mergeCell ref="CA37:CE37"/>
+    <mergeCell ref="H43:R43"/>
+    <mergeCell ref="CA46:CE46"/>
+    <mergeCell ref="CA47:CE47"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="P22:U22"/>
+    <mergeCell ref="CA24:CE24"/>
+    <mergeCell ref="CA25:CE25"/>
+    <mergeCell ref="AQ22:AV22"/>
+    <mergeCell ref="P26:U26"/>
+    <mergeCell ref="Y22:AD22"/>
+    <mergeCell ref="AH22:AM22"/>
+    <mergeCell ref="AZ34:BE34"/>
+    <mergeCell ref="AQ38:AV38"/>
+    <mergeCell ref="AZ38:BE38"/>
+    <mergeCell ref="BI38:BN38"/>
+    <mergeCell ref="BR38:BW38"/>
+    <mergeCell ref="CA21:CE21"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="P10:U10"/>
+    <mergeCell ref="Y10:AD10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="AQ10:AV10"/>
+    <mergeCell ref="AZ14:BE14"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="P18:U18"/>
+    <mergeCell ref="Y18:AD18"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="AQ18:AV18"/>
+    <mergeCell ref="AZ18:BE18"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="P14:U14"/>
+    <mergeCell ref="Y14:AD14"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="CA8:CE8"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A22:A29"/>
+    <mergeCell ref="CA9:CE9"/>
+    <mergeCell ref="CA12:CE12"/>
+    <mergeCell ref="CA13:CE13"/>
+    <mergeCell ref="CA16:CE16"/>
+    <mergeCell ref="CA17:CE17"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="AZ22:BE22"/>
+    <mergeCell ref="AZ10:BE10"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="CA20:CE20"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="A1:CF3"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="AZ6:BE6"/>
+    <mergeCell ref="AH14:AM14"/>
+    <mergeCell ref="AQ14:AV14"/>
+    <mergeCell ref="BI6:BN6"/>
+    <mergeCell ref="BI10:BN10"/>
+    <mergeCell ref="BI14:BN14"/>
+    <mergeCell ref="BR6:BW6"/>
+    <mergeCell ref="BR10:BW10"/>
+    <mergeCell ref="BR14:BW14"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="Y6:AD6"/>
     <mergeCell ref="AH6:AM6"/>
@@ -4828,74 +5741,6 @@
     <mergeCell ref="P30:U30"/>
     <mergeCell ref="Y30:AD30"/>
     <mergeCell ref="AH30:AM30"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="A1:BN3"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="AZ6:BE6"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="BI8:BM8"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="A22:A29"/>
-    <mergeCell ref="BI9:BM9"/>
-    <mergeCell ref="BI12:BM12"/>
-    <mergeCell ref="BI13:BM13"/>
-    <mergeCell ref="BI16:BM16"/>
-    <mergeCell ref="BI17:BM17"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="AZ22:BE22"/>
-    <mergeCell ref="AZ10:BE10"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="BI20:BM20"/>
-    <mergeCell ref="BI21:BM21"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="P10:U10"/>
-    <mergeCell ref="Y10:AD10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="AQ10:AV10"/>
-    <mergeCell ref="AZ14:BE14"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="P18:U18"/>
-    <mergeCell ref="Y18:AD18"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="AQ18:AV18"/>
-    <mergeCell ref="AZ18:BE18"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="P14:U14"/>
-    <mergeCell ref="Y14:AD14"/>
-    <mergeCell ref="AH14:AM14"/>
-    <mergeCell ref="AQ14:AV14"/>
-    <mergeCell ref="H39:R39"/>
-    <mergeCell ref="BI42:BM42"/>
-    <mergeCell ref="BI43:BM43"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="P22:U22"/>
-    <mergeCell ref="BI24:BM24"/>
-    <mergeCell ref="BI25:BM25"/>
-    <mergeCell ref="AQ22:AV22"/>
-    <mergeCell ref="P26:U26"/>
-    <mergeCell ref="Y22:AD22"/>
-    <mergeCell ref="AH22:AM22"/>
-    <mergeCell ref="AZ34:BE34"/>
-    <mergeCell ref="BI46:BM46"/>
-    <mergeCell ref="BI47:BM47"/>
-    <mergeCell ref="Y26:AD26"/>
-    <mergeCell ref="AH26:AM26"/>
-    <mergeCell ref="AQ26:AV26"/>
-    <mergeCell ref="BI32:BM32"/>
-    <mergeCell ref="BI33:BM33"/>
-    <mergeCell ref="AZ26:BE26"/>
-    <mergeCell ref="BI44:BM44"/>
-    <mergeCell ref="BI28:BM28"/>
-    <mergeCell ref="BI29:BM29"/>
-    <mergeCell ref="AQ30:AV30"/>
-    <mergeCell ref="AZ30:BE30"/>
-    <mergeCell ref="BI45:BM45"/>
-    <mergeCell ref="BI36:BM36"/>
-    <mergeCell ref="BI37:BM37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4916,60 +5761,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
+      <c r="A1" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
+      <c r="A2" s="60"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="67" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B3" s="68"/>
       <c r="C3" s="68"/>
@@ -4996,7 +5841,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="85" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B4" s="69"/>
       <c r="C4" s="69"/>
@@ -5023,7 +5868,7 @@
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="74" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B5" s="74"/>
       <c r="C5" s="74"/>
@@ -5036,7 +5881,7 @@
       <c r="J5" s="74"/>
       <c r="K5" s="14"/>
       <c r="L5" s="75" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M5" s="75"/>
       <c r="N5" s="75"/>
@@ -5047,7 +5892,7 @@
       <c r="S5" s="75"/>
       <c r="T5" s="75"/>
       <c r="U5" s="70" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="V5" s="71"/>
       <c r="W5" s="71"/>
@@ -5058,12 +5903,12 @@
       <c r="C6" s="77"/>
       <c r="D6" s="78"/>
       <c r="E6" s="79" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F6" s="79"/>
       <c r="G6" s="80"/>
       <c r="H6" s="81" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I6" s="79"/>
       <c r="J6" s="80"/>
@@ -5072,12 +5917,12 @@
       <c r="M6" s="83"/>
       <c r="N6" s="84"/>
       <c r="O6" s="75" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P6" s="75"/>
       <c r="Q6" s="75"/>
       <c r="R6" s="82" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S6" s="83"/>
       <c r="T6" s="84"/>
@@ -5087,7 +5932,7 @@
     </row>
     <row r="7" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>2</v>
@@ -5099,25 +5944,25 @@
         <v>3</v>
       </c>
       <c r="E7" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="J7" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="J7" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="K7" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L7" s="15" t="s">
         <v>2</v>
@@ -5129,31 +5974,31 @@
         <v>3</v>
       </c>
       <c r="O7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="S7" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="P7" s="16" t="s">
+      <c r="T7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="U7" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="R7" s="17" t="s">
+      <c r="V7" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="S7" s="17" t="s">
+      <c r="W7" s="18" t="s">
         <v>90</v>
-      </c>
-      <c r="T7" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="U7" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="V7" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="W7" s="18" t="s">
-        <v>94</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -5804,7 +6649,7 @@
     </row>
     <row r="33" spans="8:20" x14ac:dyDescent="0.25">
       <c r="H33" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I33">
         <f>SUM(I8:I32)</f>
@@ -5815,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="S33">
         <f>SUM(S8:S32)</f>
@@ -5849,6 +6694,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000D056AFC88326C4799448B54C880494B" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4e1e4b56ebf0b63f67924dd21a513bd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="26ff3a126252e742cc2543983a566b0e">
     <xsd:element name="properties">
@@ -5962,16 +6816,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D9287C-CE41-4A48-B358-97A71E5FD6DC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5985,12 +6838,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/plantillas/excel_base.xlsx
+++ b/plantillas/excel_base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estudiante\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB036A0-9BCD-43CB-B3B0-500D2035960D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0B3FB0-F43A-4400-979C-9CB1E2BFC516}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="570" activeTab="1" xr2:uid="{73D17D42-2032-4221-9DBF-D2EB2D99B5D8}"/>
   </bookViews>
@@ -679,6 +679,18 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -688,6 +700,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -697,60 +739,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -760,33 +760,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -842,15 +851,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1334,38 +1334,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
     </row>
     <row r="2" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
     </row>
     <row r="3" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -1377,25 +1377,25 @@
       <c r="C3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="51"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="47"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="32"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="39" t="s">
         <v>6</v>
       </c>
@@ -1405,20 +1405,20 @@
       <c r="E4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="37"/>
+      <c r="G4" s="54"/>
       <c r="H4" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="37"/>
+      <c r="K4" s="54"/>
       <c r="L4" s="9" t="s">
         <v>10</v>
       </c>
@@ -1430,8 +1430,8 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="39"/>
       <c r="D5" s="4" t="s">
         <v>14</v>
@@ -1443,11 +1443,11 @@
       <c r="G5" s="5">
         <v>3</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="35">
         <f>(G5+G6+G7)*16</f>
         <v>144</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="48">
         <f>H5/48</f>
         <v>3</v>
       </c>
@@ -1457,11 +1457,11 @@
       <c r="K5" s="5">
         <v>4</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="35">
         <f>(K5+K6+K7)*16</f>
         <v>144</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="48">
         <f>L5/48</f>
         <v>3</v>
       </c>
@@ -1470,8 +1470,8 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
-      <c r="B6" s="32"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="39"/>
       <c r="D6" s="4" t="s">
         <v>17</v>
@@ -1483,21 +1483,21 @@
       <c r="G6" s="5">
         <v>2</v>
       </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="49"/>
       <c r="J6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K6" s="5">
         <v>1</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="35"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="49"/>
       <c r="N6" s="43"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="40"/>
       <c r="D7" s="4" t="s">
         <v>19</v>
@@ -1509,39 +1509,39 @@
       <c r="G7" s="5">
         <v>4</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="36"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="50"/>
       <c r="J7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K7" s="5">
         <v>4</v>
       </c>
-      <c r="L7" s="33"/>
-      <c r="M7" s="36"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="50"/>
       <c r="N7" s="44"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="54"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="34"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="31"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="38" t="s">
         <v>22</v>
       </c>
@@ -1574,8 +1574,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="32"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="39"/>
       <c r="D10" s="4" t="s">
         <v>14</v>
@@ -1589,11 +1589,11 @@
       <c r="G10" s="5">
         <v>2</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="35">
         <f>(G10+G11+G12)*16</f>
         <v>96</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="48">
         <f>H10/48</f>
         <v>2</v>
       </c>
@@ -1603,11 +1603,11 @@
       <c r="K10" s="5">
         <v>0</v>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="35">
         <f>(K10+K11+K12)*16</f>
         <v>0</v>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="48">
         <f>L10/48</f>
         <v>0</v>
       </c>
@@ -1616,8 +1616,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="32"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="39"/>
       <c r="D11" s="4" t="s">
         <v>17</v>
@@ -1629,21 +1629,21 @@
       <c r="G11" s="5">
         <v>2</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="35"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="49"/>
       <c r="J11" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
-      <c r="L11" s="32"/>
-      <c r="M11" s="35"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="49"/>
       <c r="N11" s="43"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="33"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="37"/>
       <c r="C12" s="40"/>
       <c r="D12" s="4" t="s">
         <v>19</v>
@@ -1655,39 +1655,39 @@
       <c r="G12" s="5">
         <v>2</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="36"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="50"/>
       <c r="J12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="5">
         <v>0</v>
       </c>
-      <c r="L12" s="33"/>
-      <c r="M12" s="36"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="50"/>
       <c r="N12" s="44"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="54"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="34"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="31"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="38" t="s">
         <v>25</v>
       </c>
@@ -1695,20 +1695,20 @@
         <v>7</v>
       </c>
       <c r="E14" s="11"/>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="48"/>
+      <c r="G14" s="53"/>
       <c r="H14" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="47" t="s">
+      <c r="J14" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="48"/>
+      <c r="K14" s="53"/>
       <c r="L14" s="9" t="s">
         <v>10</v>
       </c>
@@ -1720,8 +1720,8 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
-      <c r="B15" s="32"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="39"/>
       <c r="D15" s="4" t="s">
         <v>14</v>
@@ -1731,11 +1731,11 @@
         <v>15</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="31">
+      <c r="H15" s="35">
         <f>(G15+G16+G17)*16</f>
         <v>0</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="48">
         <f>H15/48</f>
         <v>0</v>
       </c>
@@ -1743,19 +1743,19 @@
         <v>15</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="31">
+      <c r="L15" s="35">
         <f>(K15+K16+K17)*16</f>
         <v>0</v>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="48">
         <f>L15/48</f>
         <v>0</v>
       </c>
       <c r="N15" s="42"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="46"/>
-      <c r="B16" s="32"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="39"/>
       <c r="D16" s="4" t="s">
         <v>17</v>
@@ -1765,19 +1765,19 @@
         <v>18</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="49"/>
       <c r="J16" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="35"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="49"/>
       <c r="N16" s="43"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="46"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="40"/>
       <c r="D17" s="4" t="s">
         <v>19</v>
@@ -1787,37 +1787,37 @@
         <v>20</v>
       </c>
       <c r="G17" s="5"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="36"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="50"/>
       <c r="J17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="36"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="50"/>
       <c r="N17" s="44"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="52"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="54"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="34"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="31"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="38" t="s">
         <v>27</v>
       </c>
@@ -1850,8 +1850,8 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
-      <c r="B20" s="32"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="39"/>
       <c r="D20" s="4" t="s">
         <v>14</v>
@@ -1861,11 +1861,11 @@
         <v>15</v>
       </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="31">
+      <c r="H20" s="35">
         <f>(G20+G21+G22)*16</f>
         <v>0</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="48">
         <f>H20/48</f>
         <v>0</v>
       </c>
@@ -1873,19 +1873,19 @@
         <v>15</v>
       </c>
       <c r="K20" s="5"/>
-      <c r="L20" s="31">
+      <c r="L20" s="35">
         <f>(K20+K21+K22)*16</f>
         <v>0</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="48">
         <f>L20/48</f>
         <v>0</v>
       </c>
       <c r="N20" s="42"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="39"/>
       <c r="D21" s="4" t="s">
         <v>17</v>
@@ -1895,19 +1895,19 @@
         <v>18</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="49"/>
       <c r="J21" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="49"/>
       <c r="N21" s="43"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="46"/>
-      <c r="B22" s="33"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="40"/>
       <c r="D22" s="4" t="s">
         <v>19</v>
@@ -1917,37 +1917,37 @@
         <v>20</v>
       </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="36"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="50"/>
       <c r="J22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K22" s="5"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="36"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="50"/>
       <c r="N22" s="44"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="54"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="31"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="38" t="s">
         <v>29</v>
       </c>
@@ -1980,8 +1980,8 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="46"/>
-      <c r="B25" s="32"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="36"/>
       <c r="C25" s="39"/>
       <c r="D25" s="4" t="s">
         <v>14</v>
@@ -1991,11 +1991,11 @@
         <v>15</v>
       </c>
       <c r="G25" s="5"/>
-      <c r="H25" s="31">
+      <c r="H25" s="35">
         <f>(G25+G26+G27)*16</f>
         <v>0</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="48">
         <f>H25/48</f>
         <v>0</v>
       </c>
@@ -2003,19 +2003,19 @@
         <v>15</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="31">
+      <c r="L25" s="35">
         <f>(K25+K26+K27)*16</f>
         <v>0</v>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="48">
         <f>L25/48</f>
         <v>0</v>
       </c>
       <c r="N25" s="42"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
-      <c r="B26" s="32"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="39"/>
       <c r="D26" s="4" t="s">
         <v>17</v>
@@ -2025,19 +2025,19 @@
         <v>18</v>
       </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="49"/>
       <c r="J26" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K26" s="5"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="35"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="49"/>
       <c r="N26" s="43"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="46"/>
-      <c r="B27" s="33"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="40"/>
       <c r="D27" s="4" t="s">
         <v>19</v>
@@ -2047,37 +2047,37 @@
         <v>20</v>
       </c>
       <c r="G27" s="5"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="36"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="50"/>
       <c r="J27" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="36"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="50"/>
       <c r="N27" s="44"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="54"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="34"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="31"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="38" t="s">
         <v>31</v>
       </c>
@@ -2110,8 +2110,8 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="46"/>
-      <c r="B30" s="32"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="36"/>
       <c r="C30" s="39"/>
       <c r="D30" s="4" t="s">
         <v>14</v>
@@ -2121,11 +2121,11 @@
         <v>15</v>
       </c>
       <c r="G30" s="5"/>
-      <c r="H30" s="31">
+      <c r="H30" s="35">
         <f>(G30+G31+G32)*16</f>
         <v>0</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="48">
         <f>H30/48</f>
         <v>0</v>
       </c>
@@ -2133,19 +2133,19 @@
         <v>15</v>
       </c>
       <c r="K30" s="5"/>
-      <c r="L30" s="31">
+      <c r="L30" s="35">
         <f>(K30+K31+K32)*16</f>
         <v>0</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="48">
         <f>L30/48</f>
         <v>0</v>
       </c>
       <c r="N30" s="42"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="46"/>
-      <c r="B31" s="32"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="39"/>
       <c r="D31" s="4" t="s">
         <v>17</v>
@@ -2155,19 +2155,19 @@
         <v>18</v>
       </c>
       <c r="G31" s="5"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="35"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="49"/>
       <c r="J31" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K31" s="5"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="35"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="49"/>
       <c r="N31" s="43"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="46"/>
-      <c r="B32" s="33"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="40"/>
       <c r="D32" s="4" t="s">
         <v>19</v>
@@ -2177,37 +2177,37 @@
         <v>20</v>
       </c>
       <c r="G32" s="5"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="36"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="50"/>
       <c r="J32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K32" s="5"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="36"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="50"/>
       <c r="N32" s="44"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="54"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="46" t="s">
+      <c r="A34" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="31"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="38" t="s">
         <v>33</v>
       </c>
@@ -2240,8 +2240,8 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="46"/>
-      <c r="B35" s="32"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="39"/>
       <c r="D35" s="4" t="s">
         <v>14</v>
@@ -2251,11 +2251,11 @@
         <v>15</v>
       </c>
       <c r="G35" s="5"/>
-      <c r="H35" s="31">
+      <c r="H35" s="35">
         <f>(G35+G36+G37)*16</f>
         <v>0</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="48">
         <f>H35/48</f>
         <v>0</v>
       </c>
@@ -2263,19 +2263,19 @@
         <v>15</v>
       </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="31">
+      <c r="L35" s="35">
         <f>(K35+K36+K37)*16</f>
         <v>0</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="48">
         <f>L35/48</f>
         <v>0</v>
       </c>
       <c r="N35" s="42"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="46"/>
-      <c r="B36" s="32"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="39"/>
       <c r="D36" s="4" t="s">
         <v>17</v>
@@ -2285,19 +2285,19 @@
         <v>18</v>
       </c>
       <c r="G36" s="5"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="35"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="49"/>
       <c r="J36" s="7" t="s">
         <v>18</v>
       </c>
       <c r="K36" s="5"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="35"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="49"/>
       <c r="N36" s="43"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="46"/>
-      <c r="B37" s="33"/>
+      <c r="A37" s="31"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="40"/>
       <c r="D37" s="4" t="s">
         <v>19</v>
@@ -2307,18 +2307,80 @@
         <v>20</v>
       </c>
       <c r="G37" s="5"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="36"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="50"/>
       <c r="J37" s="7" t="s">
         <v>20</v>
       </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="36"/>
+      <c r="L37" s="37"/>
+      <c r="M37" s="50"/>
       <c r="N37" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="L20:L22"/>
+    <mergeCell ref="M20:M22"/>
+    <mergeCell ref="M30:M32"/>
+    <mergeCell ref="L25:L27"/>
+    <mergeCell ref="M25:M27"/>
+    <mergeCell ref="L30:L32"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="I30:I32"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="L10:L12"/>
+    <mergeCell ref="M10:M12"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="H35:H37"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="N25:N27"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="I35:I37"/>
+    <mergeCell ref="L35:L37"/>
+    <mergeCell ref="M35:M37"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="N15:N17"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="N30:N32"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="N10:N12"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A29:A32"/>
     <mergeCell ref="A34:A37"/>
@@ -2335,68 +2397,6 @@
     <mergeCell ref="C34:C37"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="N35:N37"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="N30:N32"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="N10:N12"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="A1:N2"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="N15:N17"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="H35:H37"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="N25:N27"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="I35:I37"/>
-    <mergeCell ref="L35:L37"/>
-    <mergeCell ref="M35:M37"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="L10:L12"/>
-    <mergeCell ref="M10:M12"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="I30:I32"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="L20:L22"/>
-    <mergeCell ref="M20:M22"/>
-    <mergeCell ref="M30:M32"/>
-    <mergeCell ref="L25:L27"/>
-    <mergeCell ref="M25:M27"/>
-    <mergeCell ref="L30:L32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2491,264 +2491,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
-      <c r="Z1" s="60"/>
-      <c r="AA1" s="60"/>
-      <c r="AB1" s="60"/>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="60"/>
-      <c r="AF1" s="60"/>
-      <c r="AG1" s="60"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="60"/>
-      <c r="AK1" s="60"/>
-      <c r="AL1" s="60"/>
-      <c r="AM1" s="60"/>
-      <c r="AN1" s="60"/>
-      <c r="AO1" s="60"/>
-      <c r="AP1" s="60"/>
-      <c r="AQ1" s="60"/>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="60"/>
-      <c r="AU1" s="60"/>
-      <c r="AV1" s="60"/>
-      <c r="AW1" s="60"/>
-      <c r="AX1" s="60"/>
-      <c r="AY1" s="60"/>
-      <c r="AZ1" s="60"/>
-      <c r="BA1" s="60"/>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
-      <c r="BG1" s="60"/>
-      <c r="BH1" s="60"/>
-      <c r="BI1" s="60"/>
-      <c r="BJ1" s="60"/>
-      <c r="BK1" s="60"/>
-      <c r="BL1" s="60"/>
-      <c r="BM1" s="60"/>
-      <c r="BN1" s="60"/>
-      <c r="BO1" s="60"/>
-      <c r="BP1" s="60"/>
-      <c r="BQ1" s="60"/>
-      <c r="BR1" s="60"/>
-      <c r="BS1" s="60"/>
-      <c r="BT1" s="60"/>
-      <c r="BU1" s="60"/>
-      <c r="BV1" s="60"/>
-      <c r="BW1" s="60"/>
-      <c r="BX1" s="60"/>
-      <c r="BY1" s="60"/>
-      <c r="BZ1" s="60"/>
-      <c r="CA1" s="60"/>
-      <c r="CB1" s="60"/>
-      <c r="CC1" s="60"/>
-      <c r="CD1" s="60"/>
-      <c r="CE1" s="60"/>
-      <c r="CF1" s="60"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+      <c r="W1" s="69"/>
+      <c r="X1" s="69"/>
+      <c r="Y1" s="69"/>
+      <c r="Z1" s="69"/>
+      <c r="AA1" s="69"/>
+      <c r="AB1" s="69"/>
+      <c r="AC1" s="69"/>
+      <c r="AD1" s="69"/>
+      <c r="AE1" s="69"/>
+      <c r="AF1" s="69"/>
+      <c r="AG1" s="69"/>
+      <c r="AH1" s="69"/>
+      <c r="AI1" s="69"/>
+      <c r="AJ1" s="69"/>
+      <c r="AK1" s="69"/>
+      <c r="AL1" s="69"/>
+      <c r="AM1" s="69"/>
+      <c r="AN1" s="69"/>
+      <c r="AO1" s="69"/>
+      <c r="AP1" s="69"/>
+      <c r="AQ1" s="69"/>
+      <c r="AR1" s="69"/>
+      <c r="AS1" s="69"/>
+      <c r="AT1" s="69"/>
+      <c r="AU1" s="69"/>
+      <c r="AV1" s="69"/>
+      <c r="AW1" s="69"/>
+      <c r="AX1" s="69"/>
+      <c r="AY1" s="69"/>
+      <c r="AZ1" s="69"/>
+      <c r="BA1" s="69"/>
+      <c r="BB1" s="69"/>
+      <c r="BC1" s="69"/>
+      <c r="BD1" s="69"/>
+      <c r="BE1" s="69"/>
+      <c r="BF1" s="69"/>
+      <c r="BG1" s="69"/>
+      <c r="BH1" s="69"/>
+      <c r="BI1" s="69"/>
+      <c r="BJ1" s="69"/>
+      <c r="BK1" s="69"/>
+      <c r="BL1" s="69"/>
+      <c r="BM1" s="69"/>
+      <c r="BN1" s="69"/>
+      <c r="BO1" s="69"/>
+      <c r="BP1" s="69"/>
+      <c r="BQ1" s="69"/>
+      <c r="BR1" s="69"/>
+      <c r="BS1" s="69"/>
+      <c r="BT1" s="69"/>
+      <c r="BU1" s="69"/>
+      <c r="BV1" s="69"/>
+      <c r="BW1" s="69"/>
+      <c r="BX1" s="69"/>
+      <c r="BY1" s="69"/>
+      <c r="BZ1" s="69"/>
+      <c r="CA1" s="69"/>
+      <c r="CB1" s="69"/>
+      <c r="CC1" s="69"/>
+      <c r="CD1" s="69"/>
+      <c r="CE1" s="69"/>
+      <c r="CF1" s="69"/>
     </row>
     <row r="2" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="60"/>
-      <c r="AI2" s="60"/>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="60"/>
-      <c r="AL2" s="60"/>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="60"/>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="60"/>
-      <c r="AT2" s="60"/>
-      <c r="AU2" s="60"/>
-      <c r="AV2" s="60"/>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="60"/>
-      <c r="AY2" s="60"/>
-      <c r="AZ2" s="60"/>
-      <c r="BA2" s="60"/>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="60"/>
-      <c r="BD2" s="60"/>
-      <c r="BE2" s="60"/>
-      <c r="BF2" s="60"/>
-      <c r="BG2" s="60"/>
-      <c r="BH2" s="60"/>
-      <c r="BI2" s="60"/>
-      <c r="BJ2" s="60"/>
-      <c r="BK2" s="60"/>
-      <c r="BL2" s="60"/>
-      <c r="BM2" s="60"/>
-      <c r="BN2" s="60"/>
-      <c r="BO2" s="60"/>
-      <c r="BP2" s="60"/>
-      <c r="BQ2" s="60"/>
-      <c r="BR2" s="60"/>
-      <c r="BS2" s="60"/>
-      <c r="BT2" s="60"/>
-      <c r="BU2" s="60"/>
-      <c r="BV2" s="60"/>
-      <c r="BW2" s="60"/>
-      <c r="BX2" s="60"/>
-      <c r="BY2" s="60"/>
-      <c r="BZ2" s="60"/>
-      <c r="CA2" s="60"/>
-      <c r="CB2" s="60"/>
-      <c r="CC2" s="60"/>
-      <c r="CD2" s="60"/>
-      <c r="CE2" s="60"/>
-      <c r="CF2" s="60"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
+      <c r="W2" s="69"/>
+      <c r="X2" s="69"/>
+      <c r="Y2" s="69"/>
+      <c r="Z2" s="69"/>
+      <c r="AA2" s="69"/>
+      <c r="AB2" s="69"/>
+      <c r="AC2" s="69"/>
+      <c r="AD2" s="69"/>
+      <c r="AE2" s="69"/>
+      <c r="AF2" s="69"/>
+      <c r="AG2" s="69"/>
+      <c r="AH2" s="69"/>
+      <c r="AI2" s="69"/>
+      <c r="AJ2" s="69"/>
+      <c r="AK2" s="69"/>
+      <c r="AL2" s="69"/>
+      <c r="AM2" s="69"/>
+      <c r="AN2" s="69"/>
+      <c r="AO2" s="69"/>
+      <c r="AP2" s="69"/>
+      <c r="AQ2" s="69"/>
+      <c r="AR2" s="69"/>
+      <c r="AS2" s="69"/>
+      <c r="AT2" s="69"/>
+      <c r="AU2" s="69"/>
+      <c r="AV2" s="69"/>
+      <c r="AW2" s="69"/>
+      <c r="AX2" s="69"/>
+      <c r="AY2" s="69"/>
+      <c r="AZ2" s="69"/>
+      <c r="BA2" s="69"/>
+      <c r="BB2" s="69"/>
+      <c r="BC2" s="69"/>
+      <c r="BD2" s="69"/>
+      <c r="BE2" s="69"/>
+      <c r="BF2" s="69"/>
+      <c r="BG2" s="69"/>
+      <c r="BH2" s="69"/>
+      <c r="BI2" s="69"/>
+      <c r="BJ2" s="69"/>
+      <c r="BK2" s="69"/>
+      <c r="BL2" s="69"/>
+      <c r="BM2" s="69"/>
+      <c r="BN2" s="69"/>
+      <c r="BO2" s="69"/>
+      <c r="BP2" s="69"/>
+      <c r="BQ2" s="69"/>
+      <c r="BR2" s="69"/>
+      <c r="BS2" s="69"/>
+      <c r="BT2" s="69"/>
+      <c r="BU2" s="69"/>
+      <c r="BV2" s="69"/>
+      <c r="BW2" s="69"/>
+      <c r="BX2" s="69"/>
+      <c r="BY2" s="69"/>
+      <c r="BZ2" s="69"/>
+      <c r="CA2" s="69"/>
+      <c r="CB2" s="69"/>
+      <c r="CC2" s="69"/>
+      <c r="CD2" s="69"/>
+      <c r="CE2" s="69"/>
+      <c r="CF2" s="69"/>
     </row>
     <row r="3" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="60"/>
-      <c r="Z3" s="60"/>
-      <c r="AA3" s="60"/>
-      <c r="AB3" s="60"/>
-      <c r="AC3" s="60"/>
-      <c r="AD3" s="60"/>
-      <c r="AE3" s="60"/>
-      <c r="AF3" s="60"/>
-      <c r="AG3" s="60"/>
-      <c r="AH3" s="60"/>
-      <c r="AI3" s="60"/>
-      <c r="AJ3" s="60"/>
-      <c r="AK3" s="60"/>
-      <c r="AL3" s="60"/>
-      <c r="AM3" s="60"/>
-      <c r="AN3" s="60"/>
-      <c r="AO3" s="60"/>
-      <c r="AP3" s="60"/>
-      <c r="AQ3" s="60"/>
-      <c r="AR3" s="60"/>
-      <c r="AS3" s="60"/>
-      <c r="AT3" s="60"/>
-      <c r="AU3" s="60"/>
-      <c r="AV3" s="60"/>
-      <c r="AW3" s="60"/>
-      <c r="AX3" s="60"/>
-      <c r="AY3" s="60"/>
-      <c r="AZ3" s="60"/>
-      <c r="BA3" s="60"/>
-      <c r="BB3" s="60"/>
-      <c r="BC3" s="60"/>
-      <c r="BD3" s="60"/>
-      <c r="BE3" s="60"/>
-      <c r="BF3" s="60"/>
-      <c r="BG3" s="60"/>
-      <c r="BH3" s="60"/>
-      <c r="BI3" s="60"/>
-      <c r="BJ3" s="60"/>
-      <c r="BK3" s="60"/>
-      <c r="BL3" s="60"/>
-      <c r="BM3" s="60"/>
-      <c r="BN3" s="60"/>
-      <c r="BO3" s="60"/>
-      <c r="BP3" s="60"/>
-      <c r="BQ3" s="60"/>
-      <c r="BR3" s="60"/>
-      <c r="BS3" s="60"/>
-      <c r="BT3" s="60"/>
-      <c r="BU3" s="60"/>
-      <c r="BV3" s="60"/>
-      <c r="BW3" s="60"/>
-      <c r="BX3" s="60"/>
-      <c r="BY3" s="60"/>
-      <c r="BZ3" s="60"/>
-      <c r="CA3" s="60"/>
-      <c r="CB3" s="60"/>
-      <c r="CC3" s="60"/>
-      <c r="CD3" s="60"/>
-      <c r="CE3" s="60"/>
-      <c r="CF3" s="60"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="69"/>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
+      <c r="W3" s="69"/>
+      <c r="X3" s="69"/>
+      <c r="Y3" s="69"/>
+      <c r="Z3" s="69"/>
+      <c r="AA3" s="69"/>
+      <c r="AB3" s="69"/>
+      <c r="AC3" s="69"/>
+      <c r="AD3" s="69"/>
+      <c r="AE3" s="69"/>
+      <c r="AF3" s="69"/>
+      <c r="AG3" s="69"/>
+      <c r="AH3" s="69"/>
+      <c r="AI3" s="69"/>
+      <c r="AJ3" s="69"/>
+      <c r="AK3" s="69"/>
+      <c r="AL3" s="69"/>
+      <c r="AM3" s="69"/>
+      <c r="AN3" s="69"/>
+      <c r="AO3" s="69"/>
+      <c r="AP3" s="69"/>
+      <c r="AQ3" s="69"/>
+      <c r="AR3" s="69"/>
+      <c r="AS3" s="69"/>
+      <c r="AT3" s="69"/>
+      <c r="AU3" s="69"/>
+      <c r="AV3" s="69"/>
+      <c r="AW3" s="69"/>
+      <c r="AX3" s="69"/>
+      <c r="AY3" s="69"/>
+      <c r="AZ3" s="69"/>
+      <c r="BA3" s="69"/>
+      <c r="BB3" s="69"/>
+      <c r="BC3" s="69"/>
+      <c r="BD3" s="69"/>
+      <c r="BE3" s="69"/>
+      <c r="BF3" s="69"/>
+      <c r="BG3" s="69"/>
+      <c r="BH3" s="69"/>
+      <c r="BI3" s="69"/>
+      <c r="BJ3" s="69"/>
+      <c r="BK3" s="69"/>
+      <c r="BL3" s="69"/>
+      <c r="BM3" s="69"/>
+      <c r="BN3" s="69"/>
+      <c r="BO3" s="69"/>
+      <c r="BP3" s="69"/>
+      <c r="BQ3" s="69"/>
+      <c r="BR3" s="69"/>
+      <c r="BS3" s="69"/>
+      <c r="BT3" s="69"/>
+      <c r="BU3" s="69"/>
+      <c r="BV3" s="69"/>
+      <c r="BW3" s="69"/>
+      <c r="BX3" s="69"/>
+      <c r="BY3" s="69"/>
+      <c r="BZ3" s="69"/>
+      <c r="CA3" s="69"/>
+      <c r="CB3" s="69"/>
+      <c r="CC3" s="69"/>
+      <c r="CD3" s="69"/>
+      <c r="CE3" s="69"/>
+      <c r="CF3" s="69"/>
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.25">
       <c r="G5" s="1"/>
@@ -2807,7 +2807,7 @@
       <c r="BW5" s="1"/>
     </row>
     <row r="6" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="66" t="s">
         <v>92</v>
       </c>
       <c r="B6" s="55" t="s">
@@ -2816,77 +2816,77 @@
       <c r="C6" s="56"/>
       <c r="D6" s="56"/>
       <c r="E6" s="57"/>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
       <c r="M6" s="1"/>
-      <c r="P6" s="58" t="s">
+      <c r="P6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="58"/>
-      <c r="U6" s="58"/>
-      <c r="Y6" s="58" t="s">
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="Y6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z6" s="58"/>
-      <c r="AA6" s="58"/>
-      <c r="AB6" s="58"/>
-      <c r="AC6" s="58"/>
-      <c r="AD6" s="58"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="62"/>
+      <c r="AB6" s="62"/>
+      <c r="AC6" s="62"/>
+      <c r="AD6" s="62"/>
       <c r="AE6" s="1"/>
-      <c r="AH6" s="58" t="s">
+      <c r="AH6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AI6" s="58"/>
-      <c r="AJ6" s="58"/>
-      <c r="AK6" s="58"/>
-      <c r="AL6" s="58"/>
-      <c r="AM6" s="58"/>
+      <c r="AI6" s="62"/>
+      <c r="AJ6" s="62"/>
+      <c r="AK6" s="62"/>
+      <c r="AL6" s="62"/>
+      <c r="AM6" s="62"/>
       <c r="AN6" s="1"/>
-      <c r="AQ6" s="58" t="s">
+      <c r="AQ6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR6" s="58"/>
-      <c r="AS6" s="58"/>
-      <c r="AT6" s="58"/>
-      <c r="AU6" s="58"/>
-      <c r="AV6" s="58"/>
+      <c r="AR6" s="62"/>
+      <c r="AS6" s="62"/>
+      <c r="AT6" s="62"/>
+      <c r="AU6" s="62"/>
+      <c r="AV6" s="62"/>
       <c r="AW6" s="1"/>
-      <c r="AZ6" s="58" t="s">
+      <c r="AZ6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA6" s="58"/>
-      <c r="BB6" s="58"/>
-      <c r="BC6" s="58"/>
-      <c r="BD6" s="58"/>
-      <c r="BE6" s="58"/>
-      <c r="BI6" s="58" t="s">
+      <c r="BA6" s="62"/>
+      <c r="BB6" s="62"/>
+      <c r="BC6" s="62"/>
+      <c r="BD6" s="62"/>
+      <c r="BE6" s="62"/>
+      <c r="BI6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ6" s="58"/>
-      <c r="BK6" s="58"/>
-      <c r="BL6" s="58"/>
-      <c r="BM6" s="58"/>
-      <c r="BN6" s="58"/>
-      <c r="BR6" s="58" t="s">
+      <c r="BJ6" s="62"/>
+      <c r="BK6" s="62"/>
+      <c r="BL6" s="62"/>
+      <c r="BM6" s="62"/>
+      <c r="BN6" s="62"/>
+      <c r="BR6" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS6" s="58"/>
-      <c r="BT6" s="58"/>
-      <c r="BU6" s="58"/>
-      <c r="BV6" s="58"/>
-      <c r="BW6" s="58"/>
+      <c r="BS6" s="62"/>
+      <c r="BT6" s="62"/>
+      <c r="BU6" s="62"/>
+      <c r="BV6" s="62"/>
+      <c r="BW6" s="62"/>
     </row>
     <row r="7" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A7" s="63"/>
+      <c r="A7" s="67"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -3114,21 +3114,21 @@
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A8" s="63"/>
-      <c r="CA8" s="61" t="s">
+      <c r="A8" s="67"/>
+      <c r="CA8" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB8" s="61"/>
-      <c r="CC8" s="61"/>
-      <c r="CD8" s="61"/>
-      <c r="CE8" s="61"/>
+      <c r="CB8" s="64"/>
+      <c r="CC8" s="64"/>
+      <c r="CD8" s="64"/>
+      <c r="CE8" s="64"/>
       <c r="CF8" s="3">
         <f>(CB7+CD7+CF7)*16</f>
         <v>816</v>
       </c>
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A9" s="63"/>
+      <c r="A9" s="67"/>
       <c r="CA9" s="55" t="s">
         <v>42</v>
       </c>
@@ -3142,84 +3142,84 @@
       </c>
     </row>
     <row r="10" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="63"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="55" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="56"/>
       <c r="E10" s="57"/>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
       <c r="M10" s="1"/>
-      <c r="P10" s="58" t="s">
+      <c r="P10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q10" s="58"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="58"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="Y10" s="58" t="s">
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="62"/>
+      <c r="Y10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z10" s="58"/>
-      <c r="AA10" s="58"/>
-      <c r="AB10" s="58"/>
-      <c r="AC10" s="58"/>
-      <c r="AD10" s="58"/>
+      <c r="Z10" s="62"/>
+      <c r="AA10" s="62"/>
+      <c r="AB10" s="62"/>
+      <c r="AC10" s="62"/>
+      <c r="AD10" s="62"/>
       <c r="AE10" s="1"/>
-      <c r="AH10" s="58" t="s">
+      <c r="AH10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AI10" s="58"/>
-      <c r="AJ10" s="58"/>
-      <c r="AK10" s="58"/>
-      <c r="AL10" s="58"/>
-      <c r="AM10" s="58"/>
+      <c r="AI10" s="62"/>
+      <c r="AJ10" s="62"/>
+      <c r="AK10" s="62"/>
+      <c r="AL10" s="62"/>
+      <c r="AM10" s="62"/>
       <c r="AN10" s="1"/>
-      <c r="AQ10" s="58" t="s">
+      <c r="AQ10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR10" s="58"/>
-      <c r="AS10" s="58"/>
-      <c r="AT10" s="58"/>
-      <c r="AU10" s="58"/>
-      <c r="AV10" s="58"/>
+      <c r="AR10" s="62"/>
+      <c r="AS10" s="62"/>
+      <c r="AT10" s="62"/>
+      <c r="AU10" s="62"/>
+      <c r="AV10" s="62"/>
       <c r="AW10" s="1"/>
-      <c r="AZ10" s="58" t="s">
+      <c r="AZ10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA10" s="58"/>
-      <c r="BB10" s="58"/>
-      <c r="BC10" s="58"/>
-      <c r="BD10" s="58"/>
-      <c r="BE10" s="58"/>
-      <c r="BI10" s="58" t="s">
+      <c r="BA10" s="62"/>
+      <c r="BB10" s="62"/>
+      <c r="BC10" s="62"/>
+      <c r="BD10" s="62"/>
+      <c r="BE10" s="62"/>
+      <c r="BI10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ10" s="58"/>
-      <c r="BK10" s="58"/>
-      <c r="BL10" s="58"/>
-      <c r="BM10" s="58"/>
-      <c r="BN10" s="58"/>
-      <c r="BR10" s="58" t="s">
+      <c r="BJ10" s="62"/>
+      <c r="BK10" s="62"/>
+      <c r="BL10" s="62"/>
+      <c r="BM10" s="62"/>
+      <c r="BN10" s="62"/>
+      <c r="BR10" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS10" s="58"/>
-      <c r="BT10" s="58"/>
-      <c r="BU10" s="58"/>
-      <c r="BV10" s="58"/>
-      <c r="BW10" s="58"/>
+      <c r="BS10" s="62"/>
+      <c r="BT10" s="62"/>
+      <c r="BU10" s="62"/>
+      <c r="BV10" s="62"/>
+      <c r="BW10" s="62"/>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A11" s="63"/>
+      <c r="A11" s="67"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -3399,21 +3399,21 @@
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A12" s="63"/>
-      <c r="CA12" s="61" t="s">
+      <c r="A12" s="67"/>
+      <c r="CA12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB12" s="61"/>
-      <c r="CC12" s="61"/>
-      <c r="CD12" s="61"/>
-      <c r="CE12" s="61"/>
+      <c r="CB12" s="64"/>
+      <c r="CC12" s="64"/>
+      <c r="CD12" s="64"/>
+      <c r="CE12" s="64"/>
       <c r="CF12" s="3">
         <f>(CB11+CD11+CF11)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A13" s="64"/>
+      <c r="A13" s="68"/>
       <c r="CA13" s="55" t="s">
         <v>42</v>
       </c>
@@ -3427,7 +3427,7 @@
       </c>
     </row>
     <row r="14" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="66" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="55" t="s">
@@ -3436,75 +3436,75 @@
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
       <c r="E14" s="57"/>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
       <c r="M14" s="1"/>
-      <c r="P14" s="58" t="s">
+      <c r="P14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="58"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="58"/>
-      <c r="Y14" s="58" t="s">
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="Y14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z14" s="58"/>
-      <c r="AA14" s="58"/>
-      <c r="AB14" s="58"/>
-      <c r="AC14" s="58"/>
-      <c r="AD14" s="58"/>
+      <c r="Z14" s="62"/>
+      <c r="AA14" s="62"/>
+      <c r="AB14" s="62"/>
+      <c r="AC14" s="62"/>
+      <c r="AD14" s="62"/>
       <c r="AE14" s="1"/>
-      <c r="AH14" s="58"/>
-      <c r="AI14" s="58"/>
-      <c r="AJ14" s="58"/>
-      <c r="AK14" s="58"/>
-      <c r="AL14" s="58"/>
-      <c r="AM14" s="58"/>
+      <c r="AH14" s="62"/>
+      <c r="AI14" s="62"/>
+      <c r="AJ14" s="62"/>
+      <c r="AK14" s="62"/>
+      <c r="AL14" s="62"/>
+      <c r="AM14" s="62"/>
       <c r="AN14" s="1"/>
-      <c r="AQ14" s="58" t="s">
+      <c r="AQ14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR14" s="58"/>
-      <c r="AS14" s="58"/>
-      <c r="AT14" s="58"/>
-      <c r="AU14" s="58"/>
-      <c r="AV14" s="58"/>
+      <c r="AR14" s="62"/>
+      <c r="AS14" s="62"/>
+      <c r="AT14" s="62"/>
+      <c r="AU14" s="62"/>
+      <c r="AV14" s="62"/>
       <c r="AW14" s="1"/>
-      <c r="AZ14" s="58" t="s">
+      <c r="AZ14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA14" s="58"/>
-      <c r="BB14" s="58"/>
-      <c r="BC14" s="58"/>
-      <c r="BD14" s="58"/>
-      <c r="BE14" s="58"/>
-      <c r="BI14" s="58" t="s">
+      <c r="BA14" s="62"/>
+      <c r="BB14" s="62"/>
+      <c r="BC14" s="62"/>
+      <c r="BD14" s="62"/>
+      <c r="BE14" s="62"/>
+      <c r="BI14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ14" s="58"/>
-      <c r="BK14" s="58"/>
-      <c r="BL14" s="58"/>
-      <c r="BM14" s="58"/>
-      <c r="BN14" s="58"/>
-      <c r="BR14" s="58" t="s">
+      <c r="BJ14" s="62"/>
+      <c r="BK14" s="62"/>
+      <c r="BL14" s="62"/>
+      <c r="BM14" s="62"/>
+      <c r="BN14" s="62"/>
+      <c r="BR14" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS14" s="58"/>
-      <c r="BT14" s="58"/>
-      <c r="BU14" s="58"/>
-      <c r="BV14" s="58"/>
-      <c r="BW14" s="58"/>
+      <c r="BS14" s="62"/>
+      <c r="BT14" s="62"/>
+      <c r="BU14" s="62"/>
+      <c r="BV14" s="62"/>
+      <c r="BW14" s="62"/>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A15" s="63"/>
+      <c r="A15" s="67"/>
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
@@ -3684,21 +3684,21 @@
       </c>
     </row>
     <row r="16" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A16" s="63"/>
-      <c r="CA16" s="61" t="s">
+      <c r="A16" s="67"/>
+      <c r="CA16" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB16" s="61"/>
-      <c r="CC16" s="61"/>
-      <c r="CD16" s="61"/>
-      <c r="CE16" s="61"/>
+      <c r="CB16" s="64"/>
+      <c r="CC16" s="64"/>
+      <c r="CD16" s="64"/>
+      <c r="CE16" s="64"/>
       <c r="CF16" s="3">
-        <f>CB15+CD15+CF15</f>
+        <f>(CB15+CD15+CF15)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A17" s="63"/>
+      <c r="A17" s="67"/>
       <c r="CA17" s="55" t="s">
         <v>42</v>
       </c>
@@ -3712,82 +3712,82 @@
       </c>
     </row>
     <row r="18" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="63"/>
+      <c r="A18" s="67"/>
       <c r="B18" s="55" t="s">
         <v>45</v>
       </c>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
       <c r="M18" s="1"/>
-      <c r="P18" s="58" t="s">
+      <c r="P18" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="Y18" s="58" t="s">
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="62"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="62"/>
+      <c r="Y18" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z18" s="58"/>
-      <c r="AA18" s="58"/>
-      <c r="AB18" s="58"/>
-      <c r="AC18" s="58"/>
-      <c r="AD18" s="58"/>
+      <c r="Z18" s="62"/>
+      <c r="AA18" s="62"/>
+      <c r="AB18" s="62"/>
+      <c r="AC18" s="62"/>
+      <c r="AD18" s="62"/>
       <c r="AE18" s="1"/>
-      <c r="AH18" s="58"/>
-      <c r="AI18" s="58"/>
-      <c r="AJ18" s="58"/>
-      <c r="AK18" s="58"/>
-      <c r="AL18" s="58"/>
-      <c r="AM18" s="58"/>
+      <c r="AH18" s="62"/>
+      <c r="AI18" s="62"/>
+      <c r="AJ18" s="62"/>
+      <c r="AK18" s="62"/>
+      <c r="AL18" s="62"/>
+      <c r="AM18" s="62"/>
       <c r="AN18" s="1"/>
-      <c r="AQ18" s="58" t="s">
+      <c r="AQ18" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR18" s="58"/>
-      <c r="AS18" s="58"/>
-      <c r="AT18" s="58"/>
-      <c r="AU18" s="58"/>
-      <c r="AV18" s="58"/>
+      <c r="AR18" s="62"/>
+      <c r="AS18" s="62"/>
+      <c r="AT18" s="62"/>
+      <c r="AU18" s="62"/>
+      <c r="AV18" s="62"/>
       <c r="AW18" s="1"/>
-      <c r="AZ18" s="58" t="s">
+      <c r="AZ18" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA18" s="58"/>
-      <c r="BB18" s="58"/>
-      <c r="BC18" s="58"/>
-      <c r="BD18" s="58"/>
-      <c r="BE18" s="58"/>
-      <c r="BI18" s="58" t="s">
+      <c r="BA18" s="62"/>
+      <c r="BB18" s="62"/>
+      <c r="BC18" s="62"/>
+      <c r="BD18" s="62"/>
+      <c r="BE18" s="62"/>
+      <c r="BI18" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ18" s="58"/>
-      <c r="BK18" s="58"/>
-      <c r="BL18" s="58"/>
-      <c r="BM18" s="58"/>
-      <c r="BN18" s="58"/>
-      <c r="BR18" s="58" t="s">
+      <c r="BJ18" s="62"/>
+      <c r="BK18" s="62"/>
+      <c r="BL18" s="62"/>
+      <c r="BM18" s="62"/>
+      <c r="BN18" s="62"/>
+      <c r="BR18" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS18" s="58"/>
-      <c r="BT18" s="58"/>
-      <c r="BU18" s="58"/>
-      <c r="BV18" s="58"/>
-      <c r="BW18" s="58"/>
+      <c r="BS18" s="62"/>
+      <c r="BT18" s="62"/>
+      <c r="BU18" s="62"/>
+      <c r="BV18" s="62"/>
+      <c r="BW18" s="62"/>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A19" s="63"/>
+      <c r="A19" s="67"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -3967,21 +3967,21 @@
       </c>
     </row>
     <row r="20" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A20" s="63"/>
-      <c r="CA20" s="61" t="s">
+      <c r="A20" s="67"/>
+      <c r="CA20" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB20" s="61"/>
-      <c r="CC20" s="61"/>
-      <c r="CD20" s="61"/>
-      <c r="CE20" s="61"/>
+      <c r="CB20" s="64"/>
+      <c r="CC20" s="64"/>
+      <c r="CD20" s="64"/>
+      <c r="CE20" s="64"/>
       <c r="CF20" s="3">
-        <f>CB19+CD19+CF19</f>
+        <f>(CB19+CD19+CF19)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A21" s="64"/>
+      <c r="A21" s="68"/>
       <c r="CA21" s="55" t="s">
         <v>42</v>
       </c>
@@ -3995,7 +3995,7 @@
       </c>
     </row>
     <row r="22" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="66" t="s">
         <v>94</v>
       </c>
       <c r="B22" s="55" t="s">
@@ -4004,75 +4004,75 @@
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
-      <c r="G22" s="58" t="s">
+      <c r="G22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
       <c r="M22" s="1"/>
-      <c r="P22" s="58" t="s">
+      <c r="P22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="58"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="58"/>
-      <c r="Y22" s="58" t="s">
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="Y22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z22" s="58"/>
-      <c r="AA22" s="58"/>
-      <c r="AB22" s="58"/>
-      <c r="AC22" s="58"/>
-      <c r="AD22" s="58"/>
+      <c r="Z22" s="62"/>
+      <c r="AA22" s="62"/>
+      <c r="AB22" s="62"/>
+      <c r="AC22" s="62"/>
+      <c r="AD22" s="62"/>
       <c r="AE22" s="1"/>
-      <c r="AH22" s="58"/>
-      <c r="AI22" s="58"/>
-      <c r="AJ22" s="58"/>
-      <c r="AK22" s="58"/>
-      <c r="AL22" s="58"/>
-      <c r="AM22" s="58"/>
+      <c r="AH22" s="62"/>
+      <c r="AI22" s="62"/>
+      <c r="AJ22" s="62"/>
+      <c r="AK22" s="62"/>
+      <c r="AL22" s="62"/>
+      <c r="AM22" s="62"/>
       <c r="AN22" s="1"/>
-      <c r="AQ22" s="58" t="s">
+      <c r="AQ22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR22" s="58"/>
-      <c r="AS22" s="58"/>
-      <c r="AT22" s="58"/>
-      <c r="AU22" s="58"/>
-      <c r="AV22" s="58"/>
+      <c r="AR22" s="62"/>
+      <c r="AS22" s="62"/>
+      <c r="AT22" s="62"/>
+      <c r="AU22" s="62"/>
+      <c r="AV22" s="62"/>
       <c r="AW22" s="1"/>
-      <c r="AZ22" s="58" t="s">
+      <c r="AZ22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA22" s="58"/>
-      <c r="BB22" s="58"/>
-      <c r="BC22" s="58"/>
-      <c r="BD22" s="58"/>
-      <c r="BE22" s="58"/>
-      <c r="BI22" s="58" t="s">
+      <c r="BA22" s="62"/>
+      <c r="BB22" s="62"/>
+      <c r="BC22" s="62"/>
+      <c r="BD22" s="62"/>
+      <c r="BE22" s="62"/>
+      <c r="BI22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ22" s="58"/>
-      <c r="BK22" s="58"/>
-      <c r="BL22" s="58"/>
-      <c r="BM22" s="58"/>
-      <c r="BN22" s="58"/>
-      <c r="BR22" s="58" t="s">
+      <c r="BJ22" s="62"/>
+      <c r="BK22" s="62"/>
+      <c r="BL22" s="62"/>
+      <c r="BM22" s="62"/>
+      <c r="BN22" s="62"/>
+      <c r="BR22" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS22" s="58"/>
-      <c r="BT22" s="58"/>
-      <c r="BU22" s="58"/>
-      <c r="BV22" s="58"/>
-      <c r="BW22" s="58"/>
+      <c r="BS22" s="62"/>
+      <c r="BT22" s="62"/>
+      <c r="BU22" s="62"/>
+      <c r="BV22" s="62"/>
+      <c r="BW22" s="62"/>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A23" s="63"/>
+      <c r="A23" s="67"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
       <c r="D23" s="23"/>
@@ -4252,21 +4252,21 @@
       </c>
     </row>
     <row r="24" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A24" s="63"/>
-      <c r="CA24" s="61" t="s">
+      <c r="A24" s="67"/>
+      <c r="CA24" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB24" s="61"/>
-      <c r="CC24" s="61"/>
-      <c r="CD24" s="61"/>
-      <c r="CE24" s="61"/>
+      <c r="CB24" s="64"/>
+      <c r="CC24" s="64"/>
+      <c r="CD24" s="64"/>
+      <c r="CE24" s="64"/>
       <c r="CF24" s="3">
-        <f>CB23+CD23+CF23</f>
+        <f>(CB23+CD23+CF23)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A25" s="63"/>
+      <c r="A25" s="67"/>
       <c r="CA25" s="55" t="s">
         <v>42</v>
       </c>
@@ -4280,82 +4280,82 @@
       </c>
     </row>
     <row r="26" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="63"/>
+      <c r="A26" s="67"/>
       <c r="B26" s="55" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="E26" s="57"/>
-      <c r="G26" s="58" t="s">
+      <c r="G26" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="62"/>
       <c r="M26" s="1"/>
-      <c r="P26" s="58" t="s">
+      <c r="P26" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="Y26" s="58" t="s">
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="62"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="62"/>
+      <c r="Y26" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="58"/>
-      <c r="AB26" s="58"/>
-      <c r="AC26" s="58"/>
-      <c r="AD26" s="58"/>
+      <c r="Z26" s="62"/>
+      <c r="AA26" s="62"/>
+      <c r="AB26" s="62"/>
+      <c r="AC26" s="62"/>
+      <c r="AD26" s="62"/>
       <c r="AE26" s="1"/>
-      <c r="AH26" s="58"/>
-      <c r="AI26" s="58"/>
-      <c r="AJ26" s="58"/>
-      <c r="AK26" s="58"/>
-      <c r="AL26" s="58"/>
-      <c r="AM26" s="58"/>
+      <c r="AH26" s="62"/>
+      <c r="AI26" s="62"/>
+      <c r="AJ26" s="62"/>
+      <c r="AK26" s="62"/>
+      <c r="AL26" s="62"/>
+      <c r="AM26" s="62"/>
       <c r="AN26" s="1"/>
-      <c r="AQ26" s="58" t="s">
+      <c r="AQ26" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR26" s="58"/>
-      <c r="AS26" s="58"/>
-      <c r="AT26" s="58"/>
-      <c r="AU26" s="58"/>
-      <c r="AV26" s="58"/>
+      <c r="AR26" s="62"/>
+      <c r="AS26" s="62"/>
+      <c r="AT26" s="62"/>
+      <c r="AU26" s="62"/>
+      <c r="AV26" s="62"/>
       <c r="AW26" s="1"/>
-      <c r="AZ26" s="58" t="s">
+      <c r="AZ26" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA26" s="58"/>
-      <c r="BB26" s="58"/>
-      <c r="BC26" s="58"/>
-      <c r="BD26" s="58"/>
-      <c r="BE26" s="58"/>
-      <c r="BI26" s="58" t="s">
+      <c r="BA26" s="62"/>
+      <c r="BB26" s="62"/>
+      <c r="BC26" s="62"/>
+      <c r="BD26" s="62"/>
+      <c r="BE26" s="62"/>
+      <c r="BI26" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ26" s="58"/>
-      <c r="BK26" s="58"/>
-      <c r="BL26" s="58"/>
-      <c r="BM26" s="58"/>
-      <c r="BN26" s="58"/>
-      <c r="BR26" s="58" t="s">
+      <c r="BJ26" s="62"/>
+      <c r="BK26" s="62"/>
+      <c r="BL26" s="62"/>
+      <c r="BM26" s="62"/>
+      <c r="BN26" s="62"/>
+      <c r="BR26" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS26" s="58"/>
-      <c r="BT26" s="58"/>
-      <c r="BU26" s="58"/>
-      <c r="BV26" s="58"/>
-      <c r="BW26" s="58"/>
+      <c r="BS26" s="62"/>
+      <c r="BT26" s="62"/>
+      <c r="BU26" s="62"/>
+      <c r="BV26" s="62"/>
+      <c r="BW26" s="62"/>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A27" s="63"/>
+      <c r="A27" s="67"/>
       <c r="B27" s="23"/>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
@@ -4535,21 +4535,21 @@
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A28" s="63"/>
-      <c r="CA28" s="61" t="s">
+      <c r="A28" s="67"/>
+      <c r="CA28" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB28" s="61"/>
-      <c r="CC28" s="61"/>
-      <c r="CD28" s="61"/>
-      <c r="CE28" s="61"/>
+      <c r="CB28" s="64"/>
+      <c r="CC28" s="64"/>
+      <c r="CD28" s="64"/>
+      <c r="CE28" s="64"/>
       <c r="CF28" s="3">
-        <f>CB27+CD27+CF27</f>
+        <f>(CB27+CD27+CF27)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A29" s="64"/>
+      <c r="A29" s="68"/>
       <c r="CA29" s="55" t="s">
         <v>42</v>
       </c>
@@ -4563,7 +4563,7 @@
       </c>
     </row>
     <row r="30" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="59" t="s">
+      <c r="A30" s="58" t="s">
         <v>95</v>
       </c>
       <c r="B30" s="55" t="s">
@@ -4572,75 +4572,75 @@
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="E30" s="57"/>
-      <c r="G30" s="58" t="s">
+      <c r="G30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
       <c r="M30" s="1"/>
-      <c r="P30" s="58" t="s">
+      <c r="P30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q30" s="58"/>
-      <c r="R30" s="58"/>
-      <c r="S30" s="58"/>
-      <c r="T30" s="58"/>
-      <c r="U30" s="58"/>
-      <c r="Y30" s="58" t="s">
+      <c r="Q30" s="62"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="62"/>
+      <c r="T30" s="62"/>
+      <c r="U30" s="62"/>
+      <c r="Y30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z30" s="58"/>
-      <c r="AA30" s="58"/>
-      <c r="AB30" s="58"/>
-      <c r="AC30" s="58"/>
-      <c r="AD30" s="58"/>
+      <c r="Z30" s="62"/>
+      <c r="AA30" s="62"/>
+      <c r="AB30" s="62"/>
+      <c r="AC30" s="62"/>
+      <c r="AD30" s="62"/>
       <c r="AE30" s="1"/>
-      <c r="AH30" s="58"/>
-      <c r="AI30" s="58"/>
-      <c r="AJ30" s="58"/>
-      <c r="AK30" s="58"/>
-      <c r="AL30" s="58"/>
-      <c r="AM30" s="58"/>
+      <c r="AH30" s="62"/>
+      <c r="AI30" s="62"/>
+      <c r="AJ30" s="62"/>
+      <c r="AK30" s="62"/>
+      <c r="AL30" s="62"/>
+      <c r="AM30" s="62"/>
       <c r="AN30" s="1"/>
-      <c r="AQ30" s="58" t="s">
+      <c r="AQ30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR30" s="58"/>
-      <c r="AS30" s="58"/>
-      <c r="AT30" s="58"/>
-      <c r="AU30" s="58"/>
-      <c r="AV30" s="58"/>
+      <c r="AR30" s="62"/>
+      <c r="AS30" s="62"/>
+      <c r="AT30" s="62"/>
+      <c r="AU30" s="62"/>
+      <c r="AV30" s="62"/>
       <c r="AW30" s="1"/>
-      <c r="AZ30" s="58" t="s">
+      <c r="AZ30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA30" s="58"/>
-      <c r="BB30" s="58"/>
-      <c r="BC30" s="58"/>
-      <c r="BD30" s="58"/>
-      <c r="BE30" s="58"/>
-      <c r="BI30" s="58" t="s">
+      <c r="BA30" s="62"/>
+      <c r="BB30" s="62"/>
+      <c r="BC30" s="62"/>
+      <c r="BD30" s="62"/>
+      <c r="BE30" s="62"/>
+      <c r="BI30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ30" s="58"/>
-      <c r="BK30" s="58"/>
-      <c r="BL30" s="58"/>
-      <c r="BM30" s="58"/>
-      <c r="BN30" s="58"/>
-      <c r="BR30" s="58" t="s">
+      <c r="BJ30" s="62"/>
+      <c r="BK30" s="62"/>
+      <c r="BL30" s="62"/>
+      <c r="BM30" s="62"/>
+      <c r="BN30" s="62"/>
+      <c r="BR30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS30" s="58"/>
-      <c r="BT30" s="58"/>
-      <c r="BU30" s="58"/>
-      <c r="BV30" s="58"/>
-      <c r="BW30" s="58"/>
+      <c r="BS30" s="62"/>
+      <c r="BT30" s="62"/>
+      <c r="BU30" s="62"/>
+      <c r="BV30" s="62"/>
+      <c r="BW30" s="62"/>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
+      <c r="A31" s="58"/>
       <c r="B31" s="23"/>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -4820,21 +4820,21 @@
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A32" s="59"/>
-      <c r="CA32" s="61" t="s">
+      <c r="A32" s="58"/>
+      <c r="CA32" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB32" s="61"/>
-      <c r="CC32" s="61"/>
-      <c r="CD32" s="61"/>
-      <c r="CE32" s="61"/>
+      <c r="CB32" s="64"/>
+      <c r="CC32" s="64"/>
+      <c r="CD32" s="64"/>
+      <c r="CE32" s="64"/>
       <c r="CF32" s="3">
-        <f>CB31+CD31+CF31</f>
+        <f>(CB31+CD31+CF31)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A33" s="59"/>
+      <c r="A33" s="58"/>
       <c r="CA33" s="55" t="s">
         <v>42</v>
       </c>
@@ -4848,82 +4848,82 @@
       </c>
     </row>
     <row r="34" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="59"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="55" t="s">
         <v>49</v>
       </c>
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
-      <c r="G34" s="58" t="s">
+      <c r="G34" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="58"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="62"/>
       <c r="M34" s="1"/>
-      <c r="P34" s="58" t="s">
+      <c r="P34" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Q34" s="58"/>
-      <c r="R34" s="58"/>
-      <c r="S34" s="58"/>
-      <c r="T34" s="58"/>
-      <c r="U34" s="58"/>
-      <c r="Y34" s="58" t="s">
+      <c r="Q34" s="62"/>
+      <c r="R34" s="62"/>
+      <c r="S34" s="62"/>
+      <c r="T34" s="62"/>
+      <c r="U34" s="62"/>
+      <c r="Y34" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="Z34" s="58"/>
-      <c r="AA34" s="58"/>
-      <c r="AB34" s="58"/>
-      <c r="AC34" s="58"/>
-      <c r="AD34" s="58"/>
+      <c r="Z34" s="62"/>
+      <c r="AA34" s="62"/>
+      <c r="AB34" s="62"/>
+      <c r="AC34" s="62"/>
+      <c r="AD34" s="62"/>
       <c r="AE34" s="1"/>
-      <c r="AH34" s="58"/>
-      <c r="AI34" s="58"/>
-      <c r="AJ34" s="58"/>
-      <c r="AK34" s="58"/>
-      <c r="AL34" s="58"/>
-      <c r="AM34" s="58"/>
+      <c r="AH34" s="62"/>
+      <c r="AI34" s="62"/>
+      <c r="AJ34" s="62"/>
+      <c r="AK34" s="62"/>
+      <c r="AL34" s="62"/>
+      <c r="AM34" s="62"/>
       <c r="AN34" s="1"/>
-      <c r="AQ34" s="58" t="s">
+      <c r="AQ34" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="AR34" s="58"/>
-      <c r="AS34" s="58"/>
-      <c r="AT34" s="58"/>
-      <c r="AU34" s="58"/>
-      <c r="AV34" s="58"/>
+      <c r="AR34" s="62"/>
+      <c r="AS34" s="62"/>
+      <c r="AT34" s="62"/>
+      <c r="AU34" s="62"/>
+      <c r="AV34" s="62"/>
       <c r="AW34" s="1"/>
-      <c r="AZ34" s="58" t="s">
+      <c r="AZ34" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BA34" s="58"/>
-      <c r="BB34" s="58"/>
-      <c r="BC34" s="58"/>
-      <c r="BD34" s="58"/>
-      <c r="BE34" s="58"/>
-      <c r="BI34" s="58" t="s">
+      <c r="BA34" s="62"/>
+      <c r="BB34" s="62"/>
+      <c r="BC34" s="62"/>
+      <c r="BD34" s="62"/>
+      <c r="BE34" s="62"/>
+      <c r="BI34" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BJ34" s="58"/>
-      <c r="BK34" s="58"/>
-      <c r="BL34" s="58"/>
-      <c r="BM34" s="58"/>
-      <c r="BN34" s="58"/>
-      <c r="BR34" s="58" t="s">
+      <c r="BJ34" s="62"/>
+      <c r="BK34" s="62"/>
+      <c r="BL34" s="62"/>
+      <c r="BM34" s="62"/>
+      <c r="BN34" s="62"/>
+      <c r="BR34" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="BS34" s="58"/>
-      <c r="BT34" s="58"/>
-      <c r="BU34" s="58"/>
-      <c r="BV34" s="58"/>
-      <c r="BW34" s="58"/>
+      <c r="BS34" s="62"/>
+      <c r="BT34" s="62"/>
+      <c r="BU34" s="62"/>
+      <c r="BV34" s="62"/>
+      <c r="BW34" s="62"/>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A35" s="59"/>
+      <c r="A35" s="58"/>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
@@ -5103,21 +5103,21 @@
       </c>
     </row>
     <row r="36" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A36" s="59"/>
-      <c r="CA36" s="61" t="s">
+      <c r="A36" s="58"/>
+      <c r="CA36" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="CB36" s="61"/>
-      <c r="CC36" s="61"/>
-      <c r="CD36" s="61"/>
-      <c r="CE36" s="61"/>
+      <c r="CB36" s="64"/>
+      <c r="CC36" s="64"/>
+      <c r="CD36" s="64"/>
+      <c r="CE36" s="64"/>
       <c r="CF36" s="3">
-        <f>CB35+CD35+CF35</f>
+        <f>(CB35+CD35+CF35)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A37" s="59"/>
+      <c r="A37" s="58"/>
       <c r="CA37" s="55" t="s">
         <v>42</v>
       </c>
@@ -5131,7 +5131,7 @@
       </c>
     </row>
     <row r="38" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="59" t="s">
+      <c r="A38" s="58" t="s">
         <v>96</v>
       </c>
       <c r="B38" s="55" t="s">
@@ -5140,75 +5140,75 @@
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
       <c r="E38" s="57"/>
-      <c r="G38" s="86" t="s">
+      <c r="G38" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="88"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="61"/>
       <c r="M38" s="1"/>
-      <c r="P38" s="86" t="s">
+      <c r="P38" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="Q38" s="87"/>
-      <c r="R38" s="87"/>
-      <c r="S38" s="87"/>
-      <c r="T38" s="87"/>
-      <c r="U38" s="88"/>
-      <c r="Y38" s="86" t="s">
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+      <c r="S38" s="60"/>
+      <c r="T38" s="60"/>
+      <c r="U38" s="61"/>
+      <c r="Y38" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="Z38" s="87"/>
-      <c r="AA38" s="87"/>
-      <c r="AB38" s="87"/>
-      <c r="AC38" s="87"/>
-      <c r="AD38" s="88"/>
+      <c r="Z38" s="60"/>
+      <c r="AA38" s="60"/>
+      <c r="AB38" s="60"/>
+      <c r="AC38" s="60"/>
+      <c r="AD38" s="61"/>
       <c r="AE38" s="1"/>
-      <c r="AH38" s="86"/>
-      <c r="AI38" s="87"/>
-      <c r="AJ38" s="87"/>
-      <c r="AK38" s="87"/>
-      <c r="AL38" s="87"/>
-      <c r="AM38" s="88"/>
+      <c r="AH38" s="59"/>
+      <c r="AI38" s="60"/>
+      <c r="AJ38" s="60"/>
+      <c r="AK38" s="60"/>
+      <c r="AL38" s="60"/>
+      <c r="AM38" s="61"/>
       <c r="AN38" s="1"/>
-      <c r="AQ38" s="86" t="s">
+      <c r="AQ38" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="AR38" s="87"/>
-      <c r="AS38" s="87"/>
-      <c r="AT38" s="87"/>
-      <c r="AU38" s="87"/>
-      <c r="AV38" s="88"/>
+      <c r="AR38" s="60"/>
+      <c r="AS38" s="60"/>
+      <c r="AT38" s="60"/>
+      <c r="AU38" s="60"/>
+      <c r="AV38" s="61"/>
       <c r="AW38" s="1"/>
-      <c r="AZ38" s="86" t="s">
+      <c r="AZ38" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="BA38" s="87"/>
-      <c r="BB38" s="87"/>
-      <c r="BC38" s="87"/>
-      <c r="BD38" s="87"/>
-      <c r="BE38" s="88"/>
-      <c r="BI38" s="86" t="s">
+      <c r="BA38" s="60"/>
+      <c r="BB38" s="60"/>
+      <c r="BC38" s="60"/>
+      <c r="BD38" s="60"/>
+      <c r="BE38" s="61"/>
+      <c r="BI38" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="BJ38" s="87"/>
-      <c r="BK38" s="87"/>
-      <c r="BL38" s="87"/>
-      <c r="BM38" s="87"/>
-      <c r="BN38" s="88"/>
-      <c r="BR38" s="86" t="s">
+      <c r="BJ38" s="60"/>
+      <c r="BK38" s="60"/>
+      <c r="BL38" s="60"/>
+      <c r="BM38" s="60"/>
+      <c r="BN38" s="61"/>
+      <c r="BR38" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="BS38" s="87"/>
-      <c r="BT38" s="87"/>
-      <c r="BU38" s="87"/>
-      <c r="BV38" s="87"/>
-      <c r="BW38" s="88"/>
+      <c r="BS38" s="60"/>
+      <c r="BT38" s="60"/>
+      <c r="BU38" s="60"/>
+      <c r="BV38" s="60"/>
+      <c r="BW38" s="61"/>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A39" s="59"/>
+      <c r="A39" s="58"/>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -5388,7 +5388,7 @@
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A40" s="59"/>
+      <c r="A40" s="58"/>
       <c r="CA40" s="55" t="s">
         <v>41</v>
       </c>
@@ -5397,12 +5397,12 @@
       <c r="CD40" s="56"/>
       <c r="CE40" s="57"/>
       <c r="CF40" s="3">
-        <f>CB39+CD39+CF39</f>
+        <f>(CB39+CD39+CF39)*16</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A41" s="59"/>
+      <c r="A41" s="58"/>
       <c r="CA41" s="55" t="s">
         <v>42</v>
       </c>
@@ -5486,26 +5486,26 @@
       <c r="P46" s="19"/>
       <c r="Q46" s="19"/>
       <c r="R46" s="19"/>
-      <c r="CA46" s="66" t="s">
+      <c r="CA46" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="CB46" s="66"/>
-      <c r="CC46" s="66"/>
-      <c r="CD46" s="66"/>
-      <c r="CE46" s="66"/>
+      <c r="CB46" s="63"/>
+      <c r="CC46" s="63"/>
+      <c r="CD46" s="63"/>
+      <c r="CE46" s="63"/>
       <c r="CF46">
         <f>CB19+CB23+CB27+CB31+CB35+CB15+CB11+CB7+CB39</f>
         <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="CA47" s="66" t="s">
+      <c r="CA47" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="CB47" s="66"/>
-      <c r="CC47" s="66"/>
-      <c r="CD47" s="66"/>
-      <c r="CE47" s="66"/>
+      <c r="CB47" s="63"/>
+      <c r="CC47" s="63"/>
+      <c r="CD47" s="63"/>
+      <c r="CE47" s="63"/>
       <c r="CF47">
         <f>CD19+CD23+CD27+CD31+CD35+CD15+CD11+CD7+CD39</f>
         <v>10</v>
@@ -5515,13 +5515,13 @@
       <c r="H48" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="CA48" s="66" t="s">
+      <c r="CA48" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="CB48" s="66"/>
-      <c r="CC48" s="66"/>
-      <c r="CD48" s="66"/>
-      <c r="CE48" s="66"/>
+      <c r="CB48" s="63"/>
+      <c r="CC48" s="63"/>
+      <c r="CD48" s="63"/>
+      <c r="CE48" s="63"/>
       <c r="CF48">
         <f>CF19+CF23+CF27+CF31+CF35+CF15+CF11+CF7+CF39</f>
         <v>24</v>
@@ -5532,39 +5532,39 @@
       <c r="H49" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="CA49" s="66" t="s">
+      <c r="CA49" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="CB49" s="66"/>
-      <c r="CC49" s="66"/>
-      <c r="CD49" s="66"/>
-      <c r="CE49" s="66"/>
+      <c r="CB49" s="63"/>
+      <c r="CC49" s="63"/>
+      <c r="CD49" s="63"/>
+      <c r="CE49" s="63"/>
     </row>
     <row r="50" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G50" s="25"/>
       <c r="H50" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="CA50" s="66" t="s">
+      <c r="CA50" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="CB50" s="66"/>
-      <c r="CC50" s="66"/>
-      <c r="CD50" s="66"/>
-      <c r="CE50" s="66"/>
+      <c r="CB50" s="63"/>
+      <c r="CC50" s="63"/>
+      <c r="CD50" s="63"/>
+      <c r="CE50" s="63"/>
     </row>
     <row r="51" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G51" s="26"/>
       <c r="H51" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="CA51" s="66" t="s">
+      <c r="CA51" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="CB51" s="66"/>
-      <c r="CC51" s="66"/>
-      <c r="CD51" s="66"/>
-      <c r="CE51" s="66"/>
+      <c r="CB51" s="63"/>
+      <c r="CC51" s="63"/>
+      <c r="CD51" s="63"/>
+      <c r="CE51" s="63"/>
     </row>
     <row r="52" spans="7:84" x14ac:dyDescent="0.25">
       <c r="G52" s="27"/>
@@ -5579,8 +5579,8 @@
       <c r="CD52" s="13"/>
       <c r="CE52" s="13"/>
       <c r="CF52">
-        <f>CF46+CF47+CF48+CF49+CF50+CF51</f>
-        <v>51</v>
+        <f>(CF46+CF47+CF48+CF49+CF50+CF51)*16</f>
+        <v>816</v>
       </c>
     </row>
     <row r="53" spans="7:84" x14ac:dyDescent="0.25">
@@ -5597,7 +5597,7 @@
       <c r="CE53" s="13"/>
       <c r="CF53">
         <f>CF52/48</f>
-        <v>1.0625</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="7:84" x14ac:dyDescent="0.25">
@@ -5629,6 +5629,96 @@
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="A1:CF3"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="AZ6:BE6"/>
+    <mergeCell ref="AH14:AM14"/>
+    <mergeCell ref="AQ14:AV14"/>
+    <mergeCell ref="BI6:BN6"/>
+    <mergeCell ref="BI10:BN10"/>
+    <mergeCell ref="BI14:BN14"/>
+    <mergeCell ref="BR6:BW6"/>
+    <mergeCell ref="BR10:BW10"/>
+    <mergeCell ref="BR14:BW14"/>
+    <mergeCell ref="Y6:AD6"/>
+    <mergeCell ref="AH6:AM6"/>
+    <mergeCell ref="AQ6:AV6"/>
+    <mergeCell ref="CA8:CE8"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A22:A29"/>
+    <mergeCell ref="CA9:CE9"/>
+    <mergeCell ref="CA12:CE12"/>
+    <mergeCell ref="CA13:CE13"/>
+    <mergeCell ref="CA16:CE16"/>
+    <mergeCell ref="CA17:CE17"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="AZ22:BE22"/>
+    <mergeCell ref="AZ10:BE10"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="CA20:CE20"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="P10:U10"/>
+    <mergeCell ref="Y10:AD10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="AQ10:AV10"/>
+    <mergeCell ref="AZ14:BE14"/>
+    <mergeCell ref="G18:L18"/>
+    <mergeCell ref="P18:U18"/>
+    <mergeCell ref="Y18:AD18"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="AQ18:AV18"/>
+    <mergeCell ref="AZ18:BE18"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="P14:U14"/>
+    <mergeCell ref="Y14:AD14"/>
+    <mergeCell ref="H43:R43"/>
+    <mergeCell ref="CA46:CE46"/>
+    <mergeCell ref="CA47:CE47"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="P22:U22"/>
+    <mergeCell ref="CA24:CE24"/>
+    <mergeCell ref="CA25:CE25"/>
+    <mergeCell ref="AQ22:AV22"/>
+    <mergeCell ref="P26:U26"/>
+    <mergeCell ref="Y22:AD22"/>
+    <mergeCell ref="AH22:AM22"/>
+    <mergeCell ref="AZ34:BE34"/>
+    <mergeCell ref="AQ38:AV38"/>
+    <mergeCell ref="AZ38:BE38"/>
+    <mergeCell ref="BI38:BN38"/>
+    <mergeCell ref="BR38:BW38"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="AQ34:AV34"/>
+    <mergeCell ref="G34:L34"/>
+    <mergeCell ref="P34:U34"/>
+    <mergeCell ref="Y34:AD34"/>
+    <mergeCell ref="AH34:AM34"/>
+    <mergeCell ref="G30:L30"/>
+    <mergeCell ref="P30:U30"/>
+    <mergeCell ref="CA50:CE50"/>
+    <mergeCell ref="CA51:CE51"/>
+    <mergeCell ref="Y26:AD26"/>
+    <mergeCell ref="AH26:AM26"/>
+    <mergeCell ref="AQ26:AV26"/>
+    <mergeCell ref="CA32:CE32"/>
+    <mergeCell ref="CA33:CE33"/>
+    <mergeCell ref="AZ26:BE26"/>
+    <mergeCell ref="CA48:CE48"/>
+    <mergeCell ref="CA28:CE28"/>
+    <mergeCell ref="CA29:CE29"/>
+    <mergeCell ref="AQ30:AV30"/>
+    <mergeCell ref="AZ30:BE30"/>
+    <mergeCell ref="CA49:CE49"/>
+    <mergeCell ref="CA36:CE36"/>
+    <mergeCell ref="CA37:CE37"/>
+    <mergeCell ref="Y30:AD30"/>
+    <mergeCell ref="AH30:AM30"/>
     <mergeCell ref="CA40:CE40"/>
     <mergeCell ref="CA41:CE41"/>
     <mergeCell ref="A38:A41"/>
@@ -5647,100 +5737,10 @@
     <mergeCell ref="BI26:BN26"/>
     <mergeCell ref="BI30:BN30"/>
     <mergeCell ref="BI34:BN34"/>
-    <mergeCell ref="CA50:CE50"/>
-    <mergeCell ref="CA51:CE51"/>
-    <mergeCell ref="Y26:AD26"/>
-    <mergeCell ref="AH26:AM26"/>
-    <mergeCell ref="AQ26:AV26"/>
-    <mergeCell ref="CA32:CE32"/>
-    <mergeCell ref="CA33:CE33"/>
-    <mergeCell ref="AZ26:BE26"/>
-    <mergeCell ref="CA48:CE48"/>
-    <mergeCell ref="CA28:CE28"/>
-    <mergeCell ref="CA29:CE29"/>
-    <mergeCell ref="AQ30:AV30"/>
-    <mergeCell ref="AZ30:BE30"/>
-    <mergeCell ref="CA49:CE49"/>
-    <mergeCell ref="CA36:CE36"/>
-    <mergeCell ref="CA37:CE37"/>
-    <mergeCell ref="H43:R43"/>
-    <mergeCell ref="CA46:CE46"/>
-    <mergeCell ref="CA47:CE47"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="P22:U22"/>
-    <mergeCell ref="CA24:CE24"/>
-    <mergeCell ref="CA25:CE25"/>
-    <mergeCell ref="AQ22:AV22"/>
-    <mergeCell ref="P26:U26"/>
-    <mergeCell ref="Y22:AD22"/>
-    <mergeCell ref="AH22:AM22"/>
-    <mergeCell ref="AZ34:BE34"/>
-    <mergeCell ref="AQ38:AV38"/>
-    <mergeCell ref="AZ38:BE38"/>
-    <mergeCell ref="BI38:BN38"/>
-    <mergeCell ref="BR38:BW38"/>
     <mergeCell ref="CA21:CE21"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="P10:U10"/>
-    <mergeCell ref="Y10:AD10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="AQ10:AV10"/>
-    <mergeCell ref="AZ14:BE14"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="P18:U18"/>
-    <mergeCell ref="Y18:AD18"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="AQ18:AV18"/>
-    <mergeCell ref="AZ18:BE18"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="P14:U14"/>
-    <mergeCell ref="Y14:AD14"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="CA8:CE8"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="A22:A29"/>
-    <mergeCell ref="CA9:CE9"/>
-    <mergeCell ref="CA12:CE12"/>
-    <mergeCell ref="CA13:CE13"/>
-    <mergeCell ref="CA16:CE16"/>
-    <mergeCell ref="CA17:CE17"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="AZ22:BE22"/>
-    <mergeCell ref="AZ10:BE10"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="CA20:CE20"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="A1:CF3"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="AZ6:BE6"/>
-    <mergeCell ref="AH14:AM14"/>
-    <mergeCell ref="AQ14:AV14"/>
-    <mergeCell ref="BI6:BN6"/>
-    <mergeCell ref="BI10:BN10"/>
-    <mergeCell ref="BI14:BN14"/>
-    <mergeCell ref="BR6:BW6"/>
-    <mergeCell ref="BR10:BW10"/>
-    <mergeCell ref="BR14:BW14"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="Y6:AD6"/>
-    <mergeCell ref="AH6:AM6"/>
-    <mergeCell ref="AQ6:AV6"/>
     <mergeCell ref="A30:A37"/>
-    <mergeCell ref="AQ34:AV34"/>
-    <mergeCell ref="G34:L34"/>
-    <mergeCell ref="P34:U34"/>
-    <mergeCell ref="Y34:AD34"/>
-    <mergeCell ref="AH34:AM34"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B34:E34"/>
-    <mergeCell ref="G30:L30"/>
-    <mergeCell ref="P30:U30"/>
-    <mergeCell ref="Y30:AD30"/>
-    <mergeCell ref="AH30:AM30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5761,174 +5761,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+      <c r="W1" s="69"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
+      <c r="W2" s="69"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
-      <c r="W4" s="69"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
       <c r="K5" s="14"/>
-      <c r="L5" s="75" t="s">
+      <c r="L5" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="75"/>
-      <c r="U5" s="70" t="s">
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="78"/>
+      <c r="U5" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="V5" s="71"/>
-      <c r="W5" s="71"/>
+      <c r="V5" s="74"/>
+      <c r="W5" s="74"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="79" t="s">
+      <c r="A6" s="79"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="79"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="81" t="s">
+      <c r="F6" s="82"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="79"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="75" t="s">
+      <c r="I6" s="82"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="86"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="82" t="s">
+      <c r="P6" s="78"/>
+      <c r="Q6" s="78"/>
+      <c r="R6" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="S6" s="83"/>
-      <c r="T6" s="84"/>
-      <c r="U6" s="72"/>
-      <c r="V6" s="73"/>
-      <c r="W6" s="73"/>
+      <c r="S6" s="86"/>
+      <c r="T6" s="87"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="76"/>
     </row>
     <row r="7" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
@@ -6694,15 +6694,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000D056AFC88326C4799448B54C880494B" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4e1e4b56ebf0b63f67924dd21a513bd2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="26ff3a126252e742cc2543983a566b0e">
     <xsd:element name="properties">
@@ -6816,15 +6807,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D9287C-CE41-4A48-B358-97A71E5FD6DC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6838,4 +6830,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29C807D-6D16-46D1-BB9C-632513C228B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>